--- a/output/yearly_surface_area_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_90_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497617667352</v>
+        <v>10.84497626733274</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907139992855</v>
+        <v>37.78907171582856</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.739877916103601</v>
+        <v>6.277294820954105</v>
       </c>
       <c r="C2" t="n">
-        <v>3.608904560811275</v>
+        <v>6.544330196509239</v>
       </c>
       <c r="D2" t="n">
-        <v>31.60540384281757</v>
+        <v>30.53529884518854</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.22690689286803</v>
+        <v>19.60059291528757</v>
       </c>
       <c r="C3" t="n">
-        <v>22.87963024747192</v>
+        <v>24.27862072602362</v>
       </c>
       <c r="D3" t="n">
-        <v>86.24162707956106</v>
+        <v>87.78297097522855</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.64703815702343</v>
+        <v>39.3347035183527</v>
       </c>
       <c r="C4" t="n">
-        <v>63.97951613806038</v>
+        <v>65.56209343730625</v>
       </c>
       <c r="D4" t="n">
-        <v>100.6978620245953</v>
+        <v>119.1910435294925</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.46058820867456</v>
+        <v>45.45491870662732</v>
       </c>
       <c r="C5" t="n">
-        <v>94.54230391896785</v>
+        <v>76.96902001294994</v>
       </c>
       <c r="D5" t="n">
-        <v>63.56816384998098</v>
+        <v>84.20940933177017</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.56737772425921</v>
+        <v>38.15856976866503</v>
       </c>
       <c r="C6" t="n">
-        <v>101.5146761145287</v>
+        <v>72.69449050865934</v>
       </c>
       <c r="D6" t="n">
-        <v>43.67304662341937</v>
+        <v>52.85042416271855</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.008861091534</v>
+        <v>25.81112889235289</v>
       </c>
       <c r="C7" t="n">
-        <v>99.47165914199108</v>
+        <v>77.01418040734529</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>40.42346172236242</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="C8" t="n">
-        <v>72.09955139988574</v>
+        <v>61.08434215823654</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>43.59843379789659</v>
+        <v>39.93749660876023</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -954,7 +954,7 @@
         <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.698930740675672</v>
+        <v>7.698557597314068</v>
       </c>
       <c r="C21" t="n">
-        <v>94.31190157327697</v>
+        <v>94.30733056709732</v>
       </c>
       <c r="D21" t="n">
-        <v>8.661297083260131</v>
+        <v>8.660877296978326</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.492878405260903</v>
+        <v>6.812347319768617</v>
       </c>
       <c r="C2" t="n">
-        <v>12.31995194059322</v>
+        <v>4.041855298384118</v>
       </c>
       <c r="D2" t="n">
-        <v>35.76997760423254</v>
+        <v>37.55872192137023</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.48707003449343</v>
+        <v>20.47925711058846</v>
       </c>
       <c r="C3" t="n">
-        <v>18.12306262039612</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D3" t="n">
-        <v>90.20788780471817</v>
+        <v>90.70857913388404</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.56671477172444</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="C4" t="n">
-        <v>60.44424265506763</v>
+        <v>62.99678668610932</v>
       </c>
       <c r="D4" t="n">
-        <v>116.8299403007789</v>
+        <v>132.2090180878052</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.45491870662732</v>
+        <v>51.61538555077607</v>
       </c>
       <c r="C5" t="n">
-        <v>105.0715480470149</v>
+        <v>97.70844026516383</v>
       </c>
       <c r="D5" t="n">
-        <v>82.85950623843081</v>
+        <v>105.2924412804704</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.38249036069132</v>
+        <v>49.3887817575443</v>
       </c>
       <c r="C6" t="n">
-        <v>125.1423981126367</v>
+        <v>96.60397409788615</v>
       </c>
       <c r="D6" t="n">
-        <v>51.92463607761381</v>
+        <v>64.6844109897096</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.35117224514665</v>
+        <v>34.91389360612931</v>
       </c>
       <c r="C7" t="n">
-        <v>121.6895914368006</v>
+        <v>90.24912120829654</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>45.99291644855457</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21.11248437982766</v>
+        <v>20.11110172149591</v>
       </c>
       <c r="C8" t="n">
-        <v>101.3899941560893</v>
+        <v>81.44578954431539</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.20624913334984</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12030697039516</v>
+        <v>56.91093266748334</v>
       </c>
       <c r="D9" t="n">
-        <v>35.94374694788421</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>39.00483628972578</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.05151821117311</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1237,7 +1237,7 @@
         <v>30.8092064546734</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.09761929554372</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.882598432746963</v>
+        <v>7.883534684807079</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4591044298039</v>
+        <v>103.4713927380929</v>
       </c>
       <c r="D21" t="n">
-        <v>9.853248040933703</v>
+        <v>9.854418356008848</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.590472338608838</v>
+        <v>7.521169162234814</v>
       </c>
       <c r="C2" t="n">
-        <v>8.839656329038281</v>
+        <v>5.459498983316512</v>
       </c>
       <c r="D2" t="n">
-        <v>43.15468383557705</v>
+        <v>41.27561872964865</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.61607989437726</v>
+        <v>21.26956401250715</v>
       </c>
       <c r="C3" t="n">
-        <v>32.05897128217959</v>
+        <v>20.19945901487813</v>
       </c>
       <c r="D3" t="n">
-        <v>95.6320438706818</v>
+        <v>97.18320524339175</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.77542612210151</v>
+        <v>37.76488893926206</v>
       </c>
       <c r="C4" t="n">
-        <v>52.71003424101125</v>
+        <v>62.30759979772807</v>
       </c>
       <c r="D4" t="n">
-        <v>131.3539158374062</v>
+        <v>144.1038732724596</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.40583132141499</v>
+        <v>54.16792958181777</v>
       </c>
       <c r="C5" t="n">
-        <v>106.6914317590221</v>
+        <v>104.8506548135594</v>
       </c>
       <c r="D5" t="n">
-        <v>99.94191629232532</v>
+        <v>122.522113490002</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>57.80137783523521</v>
       </c>
       <c r="C6" t="n">
-        <v>143.8996697499763</v>
+        <v>121.6405040515883</v>
       </c>
       <c r="D6" t="n">
-        <v>63.31585468998956</v>
+        <v>79.37626538376313</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.39405034896402</v>
+        <v>45.03473068920969</v>
       </c>
       <c r="C7" t="n">
-        <v>146.961740839522</v>
+        <v>112.7065999429423</v>
       </c>
       <c r="D7" t="n">
-        <v>46.05280305851362</v>
+        <v>51.92169083450106</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.12354564648163</v>
+        <v>27.70492021384499</v>
       </c>
       <c r="C8" t="n">
-        <v>128.6776715956294</v>
+        <v>98.3858461810941</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>41.47393176590651</v>
       </c>
     </row>
     <row r="9">
@@ -1500,10 +1500,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.08749871886498</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>91.0796797660893</v>
+        <v>76.99061846244334</v>
       </c>
       <c r="D9" t="n">
         <v>36.94218436310322</v>
@@ -1517,7 +1517,7 @@
         <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>56.65666001208344</v>
+        <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
         <v>36.30012136452581</v>
@@ -1531,7 +1531,7 @@
         <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>39.626282586514</v>
+        <v>38.02701557629594</v>
       </c>
       <c r="D11" t="n">
         <v>37.13853390395258</v>
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.62976760897449</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.95941385342317</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>31.65056423721292</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>19.25796296650543</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.050708016820336</v>
+        <v>8.053375745458554</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7035737333822</v>
+        <v>111.7405884682374</v>
       </c>
       <c r="D21" t="n">
-        <v>11.06972352312796</v>
+        <v>11.07339165000551</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.987679248201297</v>
+        <v>6.895795874629596</v>
       </c>
       <c r="C2" t="n">
-        <v>5.939573610693203</v>
+        <v>3.667809423066083</v>
       </c>
       <c r="D2" t="n">
-        <v>35.2575053026157</v>
+        <v>33.43636331123786</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.37126486312131</v>
+        <v>26.14394136409256</v>
       </c>
       <c r="C3" t="n">
-        <v>44.60570694245383</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D3" t="n">
-        <v>103.1669575007761</v>
+        <v>107.7075406329176</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.81148874525138</v>
+        <v>26.0231863964702</v>
       </c>
       <c r="C4" t="n">
-        <v>82.60032484450963</v>
+        <v>87.6288365856618</v>
       </c>
       <c r="D4" t="n">
-        <v>122.4200117287603</v>
+        <v>138.8711580088241</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.31146036862028</v>
+        <v>32.54493639578177</v>
       </c>
       <c r="C5" t="n">
-        <v>85.97655519941443</v>
+        <v>72.67387380687015</v>
       </c>
       <c r="D5" t="n">
-        <v>65.65437772150545</v>
+        <v>81.53414683769762</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.17615911188346</v>
+        <v>27.93464917663875</v>
       </c>
       <c r="C6" t="n">
-        <v>96.76498072138264</v>
+        <v>74.22405343187586</v>
       </c>
       <c r="D6" t="n">
-        <v>30.30949687321178</v>
+        <v>34.17365583712723</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.28348840681585</v>
+        <v>18.32530264747096</v>
       </c>
       <c r="C7" t="n">
-        <v>90.48866764813275</v>
+        <v>69.16903450270902</v>
       </c>
       <c r="D7" t="n">
-        <v>28.26647990067416</v>
+        <v>29.16477905005999</v>
       </c>
     </row>
     <row r="8">
@@ -1797,10 +1797,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>67.09263810822702</v>
+        <v>56.74501730546564</v>
       </c>
       <c r="D8" t="n">
         <v>27.20422888467911</v>
@@ -1814,7 +1814,7 @@
         <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>43.26562132615692</v>
+        <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
         <v>27.62343515439249</v>
@@ -1828,7 +1828,7 @@
         <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
         <v>29.04009709162065</v>
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.66110142005238</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>16.58662746324986</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.66879117077033</v>
+        <v>4.248022316275948</v>
       </c>
       <c r="C2" t="n">
-        <v>3.105267988532661</v>
+        <v>1.724930716361646</v>
       </c>
       <c r="D2" t="n">
-        <v>24.87945032102267</v>
+        <v>23.13684814598458</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.09775816426395</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="C3" t="n">
-        <v>34.18936380039517</v>
+        <v>23.44904391593506</v>
       </c>
       <c r="D3" t="n">
-        <v>107.1675793955818</v>
+        <v>109.5875874865502</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.72437524148068</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="C4" t="n">
-        <v>99.75342073310991</v>
+        <v>86.62058169340033</v>
       </c>
       <c r="D4" t="n">
-        <v>143.4402118243887</v>
+        <v>158.9979676935879</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.011266555299</v>
+        <v>36.93825737228624</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3742294395592</v>
+        <v>115.1344620155447</v>
       </c>
       <c r="D5" t="n">
-        <v>86.09927366244528</v>
+        <v>103.7707323388879</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.77113927838603</v>
+        <v>33.93214590188251</v>
       </c>
       <c r="C6" t="n">
-        <v>116.9713119701905</v>
+        <v>94.67189461592844</v>
       </c>
       <c r="D6" t="n">
-        <v>38.23907308041327</v>
+        <v>44.31707311740527</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.08575620763474</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>113.0659196026967</v>
+        <v>85.87739868128548</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>32.03933632809466</v>
       </c>
     </row>
     <row r="8">
@@ -2108,10 +2108,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>86.28580572625216</v>
+        <v>72.34989706446869</v>
       </c>
       <c r="D8" t="n">
         <v>28.37250865273282</v>
@@ -2125,7 +2125,7 @@
         <v>4.548437113775471</v>
       </c>
       <c r="C9" t="n">
-        <v>49.47812079863073</v>
+        <v>44.5968712131156</v>
       </c>
       <c r="D9" t="n">
         <v>28.6218725696115</v>
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2153,7 +2153,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>29.67528785626833</v>
       </c>
       <c r="D11" t="n">
         <v>29.49759152179966</v>
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.686462629446773</v>
+        <v>3.967242472861361</v>
       </c>
       <c r="C2" t="n">
-        <v>2.900082718345077</v>
+        <v>2.835287369864788</v>
       </c>
       <c r="D2" t="n">
-        <v>27.77756954395925</v>
+        <v>18.06710300125405</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.73388961888688</v>
+        <v>19.99820073550753</v>
       </c>
       <c r="C3" t="n">
-        <v>22.21204180858409</v>
+        <v>14.46114368355552</v>
       </c>
       <c r="D3" t="n">
-        <v>103.2994934408494</v>
+        <v>102.9215205747144</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.07195498651306</v>
+        <v>43.30390948662256</v>
       </c>
       <c r="C4" t="n">
-        <v>93.20614529348792</v>
+        <v>72.00726711568656</v>
       </c>
       <c r="D4" t="n">
-        <v>161.142104679663</v>
+        <v>175.9213346193945</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.50905369908114</v>
+        <v>45.52854978444584</v>
       </c>
       <c r="C5" t="n">
-        <v>150.4528356758237</v>
+        <v>137.4201349019473</v>
       </c>
       <c r="D5" t="n">
-        <v>111.7965198211056</v>
+        <v>133.5667751627786</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.88309957439917</v>
+        <v>41.70071548558752</v>
       </c>
       <c r="C6" t="n">
-        <v>151.7487426454295</v>
+        <v>138.0229279923549</v>
       </c>
       <c r="D6" t="n">
-        <v>53.53470231257858</v>
+        <v>63.03409309887072</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>139.2962547647629</v>
+        <v>110.9100016441706</v>
       </c>
       <c r="D7" t="n">
-        <v>34.55457394637499</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.85107744859075</v>
+        <v>12.60073178400781</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4107340310655</v>
+        <v>92.46099878596459</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -2436,7 +2436,7 @@
         <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>75.32655610374501</v>
+        <v>64.6765570080756</v>
       </c>
       <c r="D9" t="n">
         <v>29.39843500367073</v>
@@ -2450,7 +2450,7 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>43.98720588877834</v>
+        <v>41.85190463204153</v>
       </c>
       <c r="D10" t="n">
         <v>30.7483380970101</v>
@@ -2464,7 +2464,7 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>34.29539255245382</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>30.03068052520567</v>
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.66637001147211</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>15.11106066376691</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.193224371287374</v>
+        <v>2.354230994783851</v>
       </c>
       <c r="C2" t="n">
-        <v>1.336158625479909</v>
+        <v>1.304742698944011</v>
       </c>
       <c r="D2" t="n">
-        <v>19.1460437282213</v>
+        <v>12.46132361000476</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.53754007803752</v>
+        <v>19.24225500323749</v>
       </c>
       <c r="C3" t="n">
-        <v>18.84464718301752</v>
+        <v>13.87209506100743</v>
       </c>
       <c r="D3" t="n">
-        <v>104.801567428347</v>
+        <v>99.03870840441823</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.76038111136832</v>
+        <v>47.69428522001429</v>
       </c>
       <c r="C4" t="n">
-        <v>89.18588844459724</v>
+        <v>65.52380527684062</v>
       </c>
       <c r="D4" t="n">
-        <v>176.3935552651372</v>
+        <v>187.8161898040488</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.71798603363646</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="C5" t="n">
-        <v>178.1381209355838</v>
+        <v>157.8895745354933</v>
       </c>
       <c r="D5" t="n">
-        <v>118.6932974434394</v>
+        <v>144.9795922246477</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.6440929139107</v>
+        <v>33.81139093426016</v>
       </c>
       <c r="C6" t="n">
-        <v>184.8356037739555</v>
+        <v>167.6078950598325</v>
       </c>
       <c r="D6" t="n">
-        <v>52.36740429222912</v>
+        <v>61.38377520803183</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.503898614185871</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>148.4589060884984</v>
+        <v>118.5156011089707</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>36.53083207502382</v>
       </c>
     </row>
     <row r="8">
@@ -2733,10 +2733,10 @@
         <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>91.96030745679872</v>
+        <v>77.52370746584938</v>
       </c>
       <c r="D8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>33.50312215512664</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
         <v>23.48831382410494</v>
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="D16" t="n">
         <v>9.506263020221864</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.29965403397353</v>
+        <v>3.692353115672254</v>
       </c>
       <c r="C2" t="n">
-        <v>5.249404974607695</v>
+        <v>2.774419012201486</v>
       </c>
       <c r="D2" t="n">
-        <v>20.02765316663493</v>
+        <v>14.59858836215007</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.04604433110836</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="C3" t="n">
-        <v>11.77115497391926</v>
+        <v>9.238245896962486</v>
       </c>
       <c r="D3" t="n">
-        <v>96.52052554302516</v>
+        <v>87.38536315500859</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.78666731520473</v>
+        <v>42.64024803855171</v>
       </c>
       <c r="C4" t="n">
-        <v>68.89316339781567</v>
+        <v>50.36169373245288</v>
       </c>
       <c r="D4" t="n">
-        <v>186.7058331505457</v>
+        <v>193.4700748328062</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.42470551197393</v>
+        <v>57.97220193577417</v>
       </c>
       <c r="C5" t="n">
-        <v>173.131207643925</v>
+        <v>141.4207567967531</v>
       </c>
       <c r="D5" t="n">
-        <v>150.0846802867312</v>
+        <v>173.7693436516855</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.74096714146165</v>
+        <v>45.96739100824416</v>
       </c>
       <c r="C6" t="n">
-        <v>230.239471599962</v>
+        <v>207.0947694723434</v>
       </c>
       <c r="D6" t="n">
-        <v>70.80266268257573</v>
+        <v>86.54106012935635</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.20552942755285</v>
+        <v>18.92416874706152</v>
       </c>
       <c r="C7" t="n">
-        <v>202.1173086118121</v>
+        <v>174.6293546406056</v>
       </c>
       <c r="D7" t="n">
-        <v>40.06414206260808</v>
+        <v>43.11835917051991</v>
       </c>
     </row>
     <row r="8">
@@ -3044,10 +3044,10 @@
         <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>135.3535559845078</v>
+        <v>111.5707178491288</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>34.13045893814036</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>63.12343213995715</v>
+        <v>56.46718270516377</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>25.0542014123786</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>24.34439782220815</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.195187866695868</v>
+        <v>2.567270246605409</v>
       </c>
       <c r="C2" t="n">
-        <v>3.916191592240526</v>
+        <v>2.89615572752809</v>
       </c>
       <c r="D2" t="n">
-        <v>14.30210055546753</v>
+        <v>11.50215610295563</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.83005983617407</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C3" t="n">
-        <v>15.88958659323463</v>
+        <v>10.18072369303943</v>
       </c>
       <c r="D3" t="n">
-        <v>91.70014431517332</v>
+        <v>81.48505945248526</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.74088502600363</v>
+        <v>37.3820073346058</v>
       </c>
       <c r="C4" t="n">
-        <v>53.62895009218627</v>
+        <v>39.6282460819225</v>
       </c>
       <c r="D4" t="n">
-        <v>191.4535650482833</v>
+        <v>193.9678209188593</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.40078371417351</v>
+        <v>62.83185307179588</v>
       </c>
       <c r="C5" t="n">
-        <v>161.3502351929633</v>
+        <v>125.8600556844411</v>
       </c>
       <c r="D5" t="n">
-        <v>172.4685279435584</v>
+        <v>194.6560260595364</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.62400029593603</v>
+        <v>54.74225198880216</v>
       </c>
       <c r="C6" t="n">
-        <v>256.4432995740136</v>
+        <v>223.839458315977</v>
       </c>
       <c r="D6" t="n">
-        <v>86.46055681760812</v>
+        <v>104.3322920257171</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>250.2661430188926</v>
+        <v>221.8200032883413</v>
       </c>
       <c r="D7" t="n">
-        <v>45.75337000871835</v>
+        <v>49.40645321622073</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>171.9874715684774</v>
+        <v>146.8694565553228</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>73.32968127330699</v>
+        <v>67.11718180083317</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.8374972116473</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>24.16670148773948</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.57426565372215</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3428,7 +3428,7 @@
         <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.179880814055419</v>
+        <v>3.863177216211199</v>
       </c>
       <c r="C2" t="n">
-        <v>8.82100312265759</v>
+        <v>4.092906179004952</v>
       </c>
       <c r="D2" t="n">
-        <v>19.87842751558942</v>
+        <v>12.88543861823939</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.694758579437254</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="C3" t="n">
-        <v>15.43798264928109</v>
+        <v>10.72068493037517</v>
       </c>
       <c r="D3" t="n">
-        <v>83.40437621428778</v>
+        <v>73.06657288856887</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.27393297168064</v>
+        <v>32.02166486941822</v>
       </c>
       <c r="C4" t="n">
-        <v>47.18377641380595</v>
+        <v>32.99163160121406</v>
       </c>
       <c r="D4" t="n">
-        <v>192.3852436196134</v>
+        <v>190.8154290405228</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.58455046131692</v>
+        <v>60.32839642596651</v>
       </c>
       <c r="C5" t="n">
-        <v>133.9594742444773</v>
+        <v>102.2490233973053</v>
       </c>
       <c r="D5" t="n">
-        <v>191.858045102433</v>
+        <v>214.4136986075034</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>66.81774875103793</v>
       </c>
       <c r="C6" t="n">
-        <v>257.4495909708666</v>
+        <v>214.8230874001744</v>
       </c>
       <c r="D6" t="n">
-        <v>111.6983450506809</v>
+        <v>131.8241729877405</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.96137734883166</v>
+        <v>34.97378021608837</v>
       </c>
       <c r="C7" t="n">
-        <v>302.7866999529843</v>
+        <v>265.2976821186156</v>
       </c>
       <c r="D7" t="n">
-        <v>55.81432048183967</v>
+        <v>62.34196096737671</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>234.2400934947677</v>
+        <v>208.6213871524472</v>
       </c>
       <c r="D8" t="n">
-        <v>37.38495257771854</v>
+        <v>39.55461500410399</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>125.6921768270148</v>
+        <v>111.6031155233689</v>
       </c>
       <c r="D9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>51.81664383014665</v>
+        <v>49.68134257340984</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>27.3318560862312</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>24.87748682561417</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.679009558440298</v>
+        <v>4.326562132615694</v>
       </c>
       <c r="C2" t="n">
-        <v>7.794095024015427</v>
+        <v>6.452045912310037</v>
       </c>
       <c r="D2" t="n">
-        <v>6.49131582047991</v>
+        <v>13.48430471782994</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.274709430739859</v>
+        <v>2.703733177495716</v>
       </c>
       <c r="C2" t="n">
-        <v>5.009858534771474</v>
+        <v>2.259983215176157</v>
       </c>
       <c r="D2" t="n">
-        <v>14.63000428868597</v>
+        <v>9.484664570728436</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.96397843457913</v>
+        <v>15.24654184695297</v>
       </c>
       <c r="C3" t="n">
-        <v>23.41959148480766</v>
+        <v>14.02426595516569</v>
       </c>
       <c r="D3" t="n">
-        <v>91.40071126537805</v>
+        <v>78.49072895453249</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.21158414469435</v>
+        <v>44.98858854711009</v>
       </c>
       <c r="C4" t="n">
-        <v>70.92243590249383</v>
+        <v>50.45103277353934</v>
       </c>
       <c r="D4" t="n">
-        <v>194.746346848327</v>
+        <v>197.8732132863531</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.64940256305943</v>
+        <v>40.42346172236243</v>
       </c>
       <c r="C5" t="n">
-        <v>210.5112514831224</v>
+        <v>168.8360614378452</v>
       </c>
       <c r="D5" t="n">
-        <v>173.3521008773806</v>
+        <v>195.0241814486289</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.20003985195487</v>
+        <v>21.69564251615027</v>
       </c>
       <c r="C6" t="n">
-        <v>249.8822796665322</v>
+        <v>221.0620940606628</v>
       </c>
       <c r="D6" t="n">
-        <v>86.70206675285282</v>
+        <v>101.1926628675358</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>164.6881773874024</v>
+        <v>146.7221943996858</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>92.62789589568656</v>
+        <v>82.19682653806419</v>
       </c>
       <c r="D8" t="n">
-        <v>24.95111790343269</v>
+        <v>25.03456645829366</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>39.49374664644068</v>
+        <v>37.94062177832222</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.85624822901923</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.63419332141022</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>19.50241814486289</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.221335201812037</v>
+        <v>5.888522730072368</v>
       </c>
       <c r="C2" t="n">
-        <v>4.771293842639499</v>
+        <v>4.16751900452771</v>
       </c>
       <c r="D2" t="n">
-        <v>11.85362178107599</v>
+        <v>18.1436793221853</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.94510424402019</v>
+        <v>9.198975988792613</v>
       </c>
       <c r="C3" t="n">
-        <v>19.63986282345744</v>
+        <v>16.25774198232718</v>
       </c>
       <c r="D3" t="n">
-        <v>8.59029241215959</v>
+        <v>14.46114368355552</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39874685604834</v>
+        <v>13.39783666637163</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1463805993119</v>
+        <v>70.14161548865147</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576323159535099</v>
+        <v>1.576216078396662</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.295146206079795</v>
+        <v>3.930917807804229</v>
       </c>
       <c r="C2" t="n">
-        <v>4.319689898685966</v>
+        <v>2.32674205906494</v>
       </c>
       <c r="D2" t="n">
-        <v>13.87111331330318</v>
+        <v>24.30807315715102</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.84188186635403</v>
+        <v>15.85031668506475</v>
       </c>
       <c r="C3" t="n">
-        <v>18.99681807717578</v>
+        <v>16.25283324380595</v>
       </c>
       <c r="D3" t="n">
-        <v>16.46881773874025</v>
+        <v>26.20775496486861</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.65236350170539</v>
+        <v>10.81002397146163</v>
       </c>
       <c r="C4" t="n">
-        <v>30.9495963763807</v>
+        <v>25.32123678793373</v>
       </c>
       <c r="D4" t="n">
-        <v>19.56524999793468</v>
+        <v>22.65382827549515</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.092505268377454</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.424156065963628</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44344919200083</v>
+        <v>15.44109649291264</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15819022905725</v>
+        <v>86.14506464467051</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251252461473859</v>
+        <v>3.250757156402661</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.271003424101125</v>
+        <v>5.636213570080939</v>
       </c>
       <c r="C2" t="n">
-        <v>5.061891163096554</v>
+        <v>3.805254101660637</v>
       </c>
       <c r="D2" t="n">
-        <v>24.83625342203581</v>
+        <v>31.09685853201772</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.73250696055514</v>
+        <v>14.5887708851076</v>
       </c>
       <c r="C3" t="n">
-        <v>17.67145867644259</v>
+        <v>11.88405595990764</v>
       </c>
       <c r="D3" t="n">
-        <v>23.74356822720911</v>
+        <v>39.56934121966769</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.43235420496287</v>
+        <v>21.99016682742431</v>
       </c>
       <c r="C4" t="n">
-        <v>40.75136545558085</v>
+        <v>34.3827680981318</v>
       </c>
       <c r="D4" t="n">
-        <v>23.43235420496287</v>
+        <v>30.69434197327653</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.67650628368406</v>
+        <v>10.03837027592364</v>
       </c>
       <c r="C5" t="n">
-        <v>34.82749980815561</v>
+        <v>28.98610096788708</v>
       </c>
       <c r="D5" t="n">
-        <v>29.47697482001049</v>
+        <v>30.55689729468198</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.8302651248191</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.38633523605029</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>9.537678946757763</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5305,10 +5305,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5322,7 +5322,7 @@
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74062778708453</v>
+        <v>16.73610988328999</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1178295012156</v>
+        <v>102.090270288069</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022188336125359</v>
+        <v>5.020832964986997</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.713771638716436</v>
+        <v>5.3711416899343</v>
       </c>
       <c r="C2" t="n">
-        <v>5.246459731494955</v>
+        <v>2.962914571416874</v>
       </c>
       <c r="D2" t="n">
-        <v>30.74146586308037</v>
+        <v>42.31627129615026</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.00877897607599</v>
+        <v>17.18058482431918</v>
       </c>
       <c r="C3" t="n">
-        <v>19.00172681569702</v>
+        <v>13.54320958008475</v>
       </c>
       <c r="D3" t="n">
-        <v>37.3358651925062</v>
+        <v>54.39864029231576</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.15906849028376</v>
+        <v>25.48715214995145</v>
       </c>
       <c r="C4" t="n">
-        <v>42.29565459436108</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D4" t="n">
-        <v>29.46912083837651</v>
+        <v>42.6274853183965</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.16924582022473</v>
+        <v>21.40209995258047</v>
       </c>
       <c r="C5" t="n">
-        <v>57.08862900195204</v>
+        <v>47.98291904506286</v>
       </c>
       <c r="D5" t="n">
-        <v>31.41592653589794</v>
+        <v>34.80295611554943</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>9.781152377410974</v>
       </c>
       <c r="C6" t="n">
-        <v>34.89818564286137</v>
+        <v>29.98748362621883</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.60133798328035</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.40538935305847</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
         <v>46.86470840992573</v>
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07083446453893</v>
+        <v>18.06461672523193</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8906819829445</v>
+        <v>117.8501186360369</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884127415062451</v>
+        <v>6.881758752469305</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.410411598104172</v>
+        <v>7.35918079103409</v>
       </c>
       <c r="C2" t="n">
-        <v>9.274570562019617</v>
+        <v>9.535715451349269</v>
       </c>
       <c r="D2" t="n">
-        <v>42.74333154749763</v>
+        <v>33.54337381100077</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.53263133951629</v>
+        <v>16.11047982669016</v>
       </c>
       <c r="C3" t="n">
-        <v>18.80046853632642</v>
+        <v>11.62389281828224</v>
       </c>
       <c r="D3" t="n">
-        <v>49.28864349171112</v>
+        <v>70.04278995948869</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.29647211114931</v>
+        <v>21.59452250261284</v>
       </c>
       <c r="C4" t="n">
-        <v>37.5351599764683</v>
+        <v>27.22288209105981</v>
       </c>
       <c r="D4" t="n">
-        <v>35.4548365911693</v>
+        <v>51.45928766580082</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.63495408493621</v>
+        <v>18.30959468420302</v>
       </c>
       <c r="C5" t="n">
-        <v>51.02633692822798</v>
+        <v>39.80986940720817</v>
       </c>
       <c r="D5" t="n">
-        <v>28.42159603794517</v>
+        <v>34.3366259560322</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.5119735799981</v>
+        <v>10.70694046251572</v>
       </c>
       <c r="C6" t="n">
-        <v>43.23027840880406</v>
+        <v>36.54850353370026</v>
       </c>
       <c r="D6" t="n">
-        <v>30.71201343195298</v>
+        <v>31.75855648468008</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>23.29589127407256</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
         <v>30.72183090899544</v>
@@ -5846,7 +5846,7 @@
         <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>22.07656062539802</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>29.84218496599028</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.47308888692249</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5916,7 +5916,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064510689769738</v>
+        <v>7.061614732675076</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22978771659129</v>
+        <v>66.20263811882883</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298383017327303</v>
+        <v>5.296211049506307</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.520948178056562</v>
+        <v>6.169302573486956</v>
       </c>
       <c r="C2" t="n">
-        <v>6.049529353568845</v>
+        <v>8.112181280191393</v>
       </c>
       <c r="D2" t="n">
-        <v>30.76110081716531</v>
+        <v>27.15023276094554</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.08870145074748</v>
+        <v>22.05005343738336</v>
       </c>
       <c r="C3" t="n">
-        <v>30.23782929080176</v>
+        <v>28.4265047764664</v>
       </c>
       <c r="D3" t="n">
-        <v>74.51955949085414</v>
+        <v>81.9661158275662</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.71612034921921</v>
+        <v>27.73339089726815</v>
       </c>
       <c r="C4" t="n">
-        <v>43.72507925174444</v>
+        <v>28.49915410658066</v>
       </c>
       <c r="D4" t="n">
-        <v>53.94801809606648</v>
+        <v>77.48247406227101</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.68528525976006</v>
+        <v>26.85079971115027</v>
       </c>
       <c r="C5" t="n">
-        <v>62.53732876052183</v>
+        <v>46.43666641087414</v>
       </c>
       <c r="D5" t="n">
-        <v>35.56381058634071</v>
+        <v>46.31394794784328</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.40758952817845</v>
+        <v>18.99878157258428</v>
       </c>
       <c r="C6" t="n">
-        <v>65.97246397768143</v>
+        <v>52.64916588334796</v>
       </c>
       <c r="D6" t="n">
-        <v>33.00635781677777</v>
+        <v>35.70321876034376</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>46.59178254814513</v>
+        <v>39.94436884268997</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>26.20284622634736</v>
+        <v>24.45042657426681</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.21114217633784</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.51874800293658</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.06249736236907</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>32.97886888105885</v>
@@ -6227,7 +6227,7 @@
         <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6255,7 +6255,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.288612369256325</v>
+        <v>7.286145115583746</v>
       </c>
       <c r="C21" t="n">
-        <v>75.61935333103438</v>
+        <v>75.59375557418137</v>
       </c>
       <c r="D21" t="n">
-        <v>6.377535823099284</v>
+        <v>6.375376976135778</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.049709280018093</v>
+        <v>5.219952543480291</v>
       </c>
       <c r="C2" t="n">
-        <v>5.261185947058657</v>
+        <v>5.071708640139023</v>
       </c>
       <c r="D2" t="n">
-        <v>29.74499194326986</v>
+        <v>28.88203571123691</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.90078672860884</v>
+        <v>21.73098543350315</v>
       </c>
       <c r="C3" t="n">
-        <v>26.1783025337412</v>
+        <v>30.38018270791754</v>
       </c>
       <c r="D3" t="n">
-        <v>81.83848862601411</v>
+        <v>84.66592201424493</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.35349559345364</v>
+        <v>36.70558316637975</v>
       </c>
       <c r="C4" t="n">
-        <v>62.15444715586556</v>
+        <v>54.05011985730815</v>
       </c>
       <c r="D4" t="n">
-        <v>78.63111887623978</v>
+        <v>100.4170821811807</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.37375244234433</v>
+        <v>34.95021827118646</v>
       </c>
       <c r="C5" t="n">
-        <v>73.21383504420589</v>
+        <v>50.11822030179968</v>
       </c>
       <c r="D5" t="n">
-        <v>47.56567627075797</v>
+        <v>64.59899893944014</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.66547037922588</v>
+        <v>28.73968229412113</v>
       </c>
       <c r="C6" t="n">
-        <v>84.85049058264335</v>
+        <v>64.64415933383549</v>
       </c>
       <c r="D6" t="n">
-        <v>37.15227837181205</v>
+        <v>42.50574860306991</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.90609637775757</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>73.84019007951534</v>
+        <v>59.82672334909638</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>36.35117224514665</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>45.64635950895544</v>
+        <v>40.63944621729671</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.06562253193106</v>
+        <v>27.95624762613216</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6496,7 +6496,7 @@
         <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.500676402540576</v>
+        <v>7.499116108221267</v>
       </c>
       <c r="C21" t="n">
-        <v>85.32019407889905</v>
+        <v>85.30244573101692</v>
       </c>
       <c r="D21" t="n">
-        <v>7.500676402540576</v>
+        <v>7.499116108221267</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_90_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626733274</v>
+        <v>10.84497618819991</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907171582856</v>
+        <v>37.789071440092</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.277294820954105</v>
+        <v>6.14672237628928</v>
       </c>
       <c r="C2" t="n">
-        <v>6.544330196509239</v>
+        <v>9.288315029879072</v>
       </c>
       <c r="D2" t="n">
-        <v>30.53529884518854</v>
+        <v>37.8728811867292</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.60059291528757</v>
+        <v>16.8369731278328</v>
       </c>
       <c r="C3" t="n">
-        <v>24.27862072602362</v>
+        <v>34.40534829532947</v>
       </c>
       <c r="D3" t="n">
-        <v>87.78297097522855</v>
+        <v>80.38550202372883</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3347035183527</v>
+        <v>31.42181702212341</v>
       </c>
       <c r="C4" t="n">
-        <v>65.56209343730625</v>
+        <v>74.03653962036472</v>
       </c>
       <c r="D4" t="n">
-        <v>119.1910435294925</v>
+        <v>86.09731016703677</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.45491870662732</v>
+        <v>41.52792788964008</v>
       </c>
       <c r="C5" t="n">
-        <v>76.96902001294994</v>
+        <v>103.9670818797373</v>
       </c>
       <c r="D5" t="n">
-        <v>84.20940933177017</v>
+        <v>60.254765348148</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.15856976866503</v>
+        <v>40.09064925062275</v>
       </c>
       <c r="C6" t="n">
-        <v>72.69449050865934</v>
+        <v>118.9838947638964</v>
       </c>
       <c r="D6" t="n">
-        <v>52.85042416271855</v>
+        <v>43.43153668817465</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.81112889235289</v>
+        <v>28.26647990067416</v>
       </c>
       <c r="C7" t="n">
-        <v>77.01418040734529</v>
+        <v>111.8083007935565</v>
       </c>
       <c r="D7" t="n">
-        <v>40.42346172236242</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.26832022289564</v>
+        <v>15.10418842983718</v>
       </c>
       <c r="C8" t="n">
-        <v>61.08434215823654</v>
+        <v>73.8519710519663</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>36.13322425480386</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>39.93749660876023</v>
+        <v>40.82499653339935</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.39062207976576</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,10 +948,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
         <v>31.03599017435442</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.698557597314068</v>
+        <v>7.693696140893261</v>
       </c>
       <c r="C21" t="n">
-        <v>94.30733056709732</v>
+        <v>94.24777772594243</v>
       </c>
       <c r="D21" t="n">
-        <v>8.660877296978326</v>
+        <v>8.655408158504917</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.812347319768617</v>
+        <v>5.648976290236146</v>
       </c>
       <c r="C2" t="n">
-        <v>4.041855298384118</v>
+        <v>10.84536688881452</v>
       </c>
       <c r="D2" t="n">
-        <v>37.55872192137023</v>
+        <v>45.82601933883262</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.47925711058846</v>
+        <v>18.78574232076272</v>
       </c>
       <c r="C3" t="n">
-        <v>24.76949457814703</v>
+        <v>35.08766294978101</v>
       </c>
       <c r="D3" t="n">
-        <v>90.70857913388404</v>
+        <v>89.80046250745575</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.00738062221102</v>
+        <v>31.34524070119216</v>
       </c>
       <c r="C4" t="n">
-        <v>62.99678668610932</v>
+        <v>79.89462817160542</v>
       </c>
       <c r="D4" t="n">
-        <v>132.2090180878052</v>
+        <v>103.5311858990516</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.61538555077607</v>
+        <v>43.98229715025711</v>
       </c>
       <c r="C5" t="n">
-        <v>97.70844026516383</v>
+        <v>118.49694790259</v>
       </c>
       <c r="D5" t="n">
-        <v>105.2924412804704</v>
+        <v>73.99923320760334</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.3887817575443</v>
+        <v>47.49695393146069</v>
       </c>
       <c r="C6" t="n">
-        <v>96.60397409788615</v>
+        <v>141.0418021829138</v>
       </c>
       <c r="D6" t="n">
-        <v>64.6844109897096</v>
+        <v>51.32086123950202</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.91389360612931</v>
+        <v>37.60879105428681</v>
       </c>
       <c r="C7" t="n">
-        <v>90.24912120829654</v>
+        <v>139.416027984681</v>
       </c>
       <c r="D7" t="n">
-        <v>45.99291644855457</v>
+        <v>41.68108053150257</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.11110172149591</v>
+        <v>22.1138670381594</v>
       </c>
       <c r="C8" t="n">
-        <v>81.44578954431539</v>
+        <v>109.1507097581604</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.20624913334984</v>
+        <v>11.09374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91093266748334</v>
+        <v>64.01093206459626</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>35.49999698556465</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>39.00483628972578</v>
+        <v>39.28954312395736</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>30.37527396939631</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,10 +1259,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>31.34327720578367</v>
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1290,7 +1290,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.86552592671396</v>
@@ -1307,7 +1307,7 @@
         <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.883534684807079</v>
+        <v>7.873395719737983</v>
       </c>
       <c r="C21" t="n">
-        <v>103.4713927380929</v>
+        <v>102.3541443565938</v>
       </c>
       <c r="D21" t="n">
-        <v>9.854418356008848</v>
+        <v>9.84174464967248</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.521169162234814</v>
+        <v>6.172247816599698</v>
       </c>
       <c r="C2" t="n">
-        <v>5.459498983316512</v>
+        <v>16.08102739556275</v>
       </c>
       <c r="D2" t="n">
-        <v>41.27561872964865</v>
+        <v>37.70205708619026</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.26956401250715</v>
+        <v>18.6679325962531</v>
       </c>
       <c r="C3" t="n">
-        <v>20.19945901487813</v>
+        <v>38.04763227808514</v>
       </c>
       <c r="D3" t="n">
-        <v>97.18320524339175</v>
+        <v>100.7714931024139</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.76488893926206</v>
+        <v>32.48112279500572</v>
       </c>
       <c r="C4" t="n">
-        <v>62.30759979772807</v>
+        <v>82.35783316156066</v>
       </c>
       <c r="D4" t="n">
-        <v>144.1038732724596</v>
+        <v>118.0934495961446</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.16792958181777</v>
+        <v>44.89041377668541</v>
       </c>
       <c r="C5" t="n">
-        <v>104.8506548135594</v>
+        <v>130.8669689760999</v>
       </c>
       <c r="D5" t="n">
-        <v>122.522113490002</v>
+        <v>89.75628386076465</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.80137783523521</v>
+        <v>52.28690098048088</v>
       </c>
       <c r="C6" t="n">
-        <v>121.6405040515883</v>
+        <v>159.8795771320016</v>
       </c>
       <c r="D6" t="n">
-        <v>79.37626538376313</v>
+        <v>59.53219903782235</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.03473068920969</v>
+        <v>45.45393695892307</v>
       </c>
       <c r="C7" t="n">
-        <v>112.7065999429423</v>
+        <v>166.2452292463379</v>
       </c>
       <c r="D7" t="n">
-        <v>51.92169083450106</v>
+        <v>45.99291644855457</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.70492021384499</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="C8" t="n">
-        <v>98.3858461810941</v>
+        <v>142.4466831476909</v>
       </c>
       <c r="D8" t="n">
-        <v>41.47393176590651</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>15.8640611529242</v>
       </c>
       <c r="C9" t="n">
-        <v>76.99061846244334</v>
+        <v>93.52030455884689</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>54.37900533823083</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02701557629594</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>27.3485457972034</v>
       </c>
       <c r="D14" t="n">
         <v>31.65056423721292</v>
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -1618,7 +1618,7 @@
         <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>19.25796296650543</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>16.24890625298896</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.053375745458554</v>
+        <v>8.03576317579774</v>
       </c>
       <c r="C21" t="n">
-        <v>111.7405884682374</v>
+        <v>110.4917436672189</v>
       </c>
       <c r="D21" t="n">
-        <v>11.07339165000551</v>
+        <v>11.04917436672189</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.895795874629596</v>
+        <v>5.772676500971245</v>
       </c>
       <c r="C2" t="n">
-        <v>3.667809423066083</v>
+        <v>11.06331487915731</v>
       </c>
       <c r="D2" t="n">
-        <v>33.43636331123786</v>
+        <v>31.12827445855362</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.14394136409256</v>
+        <v>22.41330008795468</v>
       </c>
       <c r="C3" t="n">
-        <v>32.31422568528377</v>
+        <v>58.60542920501334</v>
       </c>
       <c r="D3" t="n">
-        <v>107.7075406329176</v>
+        <v>105.8520374718911</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.0231863964702</v>
+        <v>21.55623434214721</v>
       </c>
       <c r="C4" t="n">
-        <v>87.6288365856618</v>
+        <v>110.3847666223986</v>
       </c>
       <c r="D4" t="n">
-        <v>138.8711580088241</v>
+        <v>109.3509862898267</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.54493639578177</v>
+        <v>29.45243112740432</v>
       </c>
       <c r="C5" t="n">
-        <v>72.67387380687015</v>
+        <v>95.52405162321466</v>
       </c>
       <c r="D5" t="n">
-        <v>81.53414683769762</v>
+        <v>59.69026041820608</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.93464917663875</v>
+        <v>28.21641076775758</v>
       </c>
       <c r="C6" t="n">
-        <v>74.22405343187586</v>
+        <v>109.4845039776043</v>
       </c>
       <c r="D6" t="n">
-        <v>34.17365583712723</v>
+        <v>30.26924521733767</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>19.70269467652924</v>
       </c>
       <c r="C7" t="n">
-        <v>69.16903450270902</v>
+        <v>100.1304118515407</v>
       </c>
       <c r="D7" t="n">
-        <v>29.16477905005999</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>56.74501730546564</v>
+        <v>68.92850631516855</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>41.49062147687869</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>27.40156017323271</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
         <v>26.01631416254048</v>
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
         <v>23.66110142005238</v>
@@ -1915,7 +1915,7 @@
         <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.58662746324986</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
         <v>13.9113649691773</v>
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>74.64718669240621</v>
+        <v>73.97468951499715</v>
       </c>
       <c r="D20" t="n">
         <v>7.397468951499714</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.248022316275948</v>
+        <v>3.575525138866883</v>
       </c>
       <c r="C2" t="n">
-        <v>1.724930716361646</v>
+        <v>5.180682635310418</v>
       </c>
       <c r="D2" t="n">
-        <v>23.13684814598458</v>
+        <v>22.24345773511998</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.78560345204247</v>
+        <v>21.8389776809703</v>
       </c>
       <c r="C3" t="n">
-        <v>23.44904391593506</v>
+        <v>51.82155256866788</v>
       </c>
       <c r="D3" t="n">
-        <v>109.5875874865502</v>
+        <v>107.5406435231956</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.66729500591412</v>
+        <v>30.83473189498382</v>
       </c>
       <c r="C4" t="n">
-        <v>86.62058169340033</v>
+        <v>131.6729838412865</v>
       </c>
       <c r="D4" t="n">
-        <v>158.9979676935879</v>
+        <v>130.9582715125948</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.93825737228624</v>
+        <v>32.15223731408305</v>
       </c>
       <c r="C5" t="n">
-        <v>115.1344620155447</v>
+        <v>145.1759417654971</v>
       </c>
       <c r="D5" t="n">
-        <v>103.7707323388879</v>
+        <v>77.80350556155973</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.93214590188251</v>
+        <v>33.32837106377072</v>
       </c>
       <c r="C6" t="n">
-        <v>94.67189461592844</v>
+        <v>130.9386365585099</v>
       </c>
       <c r="D6" t="n">
-        <v>44.31707311740527</v>
+        <v>37.27303333943441</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>85.87739868128548</v>
+        <v>125.5223344741802</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C8" t="n">
-        <v>72.34989706446869</v>
+        <v>89.79064503041327</v>
       </c>
       <c r="D8" t="n">
-        <v>28.37250865273282</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.548437113775471</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>44.5968712131156</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>28.6218725696115</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>29.14219885286231</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.67528785626833</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.65044106402591</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -2212,7 +2212,7 @@
         <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
         <v>11.8055161435679</v>
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.99562501195582</v>
+        <v>64.39381366925254</v>
       </c>
       <c r="D19" t="n">
         <v>6.018113427032947</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.967242472861361</v>
+        <v>3.227004703859266</v>
       </c>
       <c r="C2" t="n">
-        <v>2.835287369864788</v>
+        <v>3.769911184307752</v>
       </c>
       <c r="D2" t="n">
-        <v>18.06710300125405</v>
+        <v>21.51303744316036</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.99820073550753</v>
+        <v>16.98423528346982</v>
       </c>
       <c r="C3" t="n">
-        <v>14.46114368355552</v>
+        <v>35.44109212330985</v>
       </c>
       <c r="D3" t="n">
-        <v>102.9215205747144</v>
+        <v>100.8107630105837</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.30390948662256</v>
+        <v>36.11849803924015</v>
       </c>
       <c r="C4" t="n">
-        <v>72.00726711568656</v>
+        <v>130.3967118257656</v>
       </c>
       <c r="D4" t="n">
-        <v>175.9213346193945</v>
+        <v>151.2254711190659</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.52854978444584</v>
+        <v>38.48451000647497</v>
       </c>
       <c r="C5" t="n">
-        <v>137.4201349019473</v>
+        <v>191.9316761802515</v>
       </c>
       <c r="D5" t="n">
-        <v>133.5667751627786</v>
+        <v>102.1508486268806</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.70071548558752</v>
+        <v>37.95731148929444</v>
       </c>
       <c r="C6" t="n">
-        <v>138.0229279923549</v>
+        <v>178.2745838664741</v>
       </c>
       <c r="D6" t="n">
-        <v>63.03409309887072</v>
+        <v>49.75104666041137</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>26.88908787161589</v>
       </c>
       <c r="C7" t="n">
-        <v>110.9100016441706</v>
+        <v>155.8848457234213</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>33.95570784678443</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>92.46099878596459</v>
+        <v>123.9211039685536</v>
       </c>
       <c r="D8" t="n">
-        <v>30.54217107911827</v>
+        <v>29.6242369756475</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>64.6765570080756</v>
+        <v>73.44061876388687</v>
       </c>
       <c r="D9" t="n">
         <v>29.39843500367073</v>
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>26.25291535926396</v>
+        <v>24.95111790343269</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.51223562190536</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.11106066376691</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>4.212679398923063</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.354230994783851</v>
+        <v>1.947787445225672</v>
       </c>
       <c r="C2" t="n">
-        <v>1.304742698944011</v>
+        <v>1.828014225307561</v>
       </c>
       <c r="D2" t="n">
-        <v>12.46132361000476</v>
+        <v>15.04332007217387</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.24225500323749</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C3" t="n">
-        <v>13.87209506100743</v>
+        <v>28.97628349084461</v>
       </c>
       <c r="D3" t="n">
-        <v>99.03870840441823</v>
+        <v>99.25469289935253</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.69428522001429</v>
+        <v>39.53890704083604</v>
       </c>
       <c r="C4" t="n">
-        <v>65.52380527684062</v>
+        <v>128.0738967575176</v>
       </c>
       <c r="D4" t="n">
-        <v>187.8161898040488</v>
+        <v>163.9754285541193</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.97662764820988</v>
+        <v>40.2761995667254</v>
       </c>
       <c r="C5" t="n">
-        <v>157.8895745354933</v>
+        <v>234.8831382410494</v>
       </c>
       <c r="D5" t="n">
-        <v>144.9795922246477</v>
+        <v>108.7285582453343</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.81139093426016</v>
+        <v>31.75855648468008</v>
       </c>
       <c r="C6" t="n">
-        <v>167.6078950598325</v>
+        <v>208.4230741161894</v>
       </c>
       <c r="D6" t="n">
-        <v>61.38377520803183</v>
+        <v>48.94601354292898</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.324238784308704</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>118.5156011089707</v>
+        <v>163.3107853583442</v>
       </c>
       <c r="D7" t="n">
-        <v>36.53083207502382</v>
+        <v>34.07548106670254</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>77.52370746584938</v>
+        <v>90.54168202416209</v>
       </c>
       <c r="D8" t="n">
-        <v>31.96079651175491</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.06093477758807</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>20.96816746730337</v>
+        <v>19.90198946049134</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.83853571261379</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.52848336452105</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.81278928812512</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>3.21031499288707</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.692353115672254</v>
+        <v>3.016910695150449</v>
       </c>
       <c r="C2" t="n">
-        <v>2.774419012201486</v>
+        <v>9.619164006210248</v>
       </c>
       <c r="D2" t="n">
-        <v>14.59858836215007</v>
+        <v>13.80533621711865</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.78864650614645</v>
+        <v>11.67298020349457</v>
       </c>
       <c r="C3" t="n">
-        <v>9.238245896962486</v>
+        <v>18.04452280405637</v>
       </c>
       <c r="D3" t="n">
-        <v>87.38536315500859</v>
+        <v>89.6630178288612</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.64024803855171</v>
+        <v>35.53141291210056</v>
       </c>
       <c r="C4" t="n">
-        <v>50.36169373245288</v>
+        <v>102.331490204462</v>
       </c>
       <c r="D4" t="n">
-        <v>193.4700748328062</v>
+        <v>173.4326041891288</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.97220193577417</v>
+        <v>48.35107443415542</v>
       </c>
       <c r="C5" t="n">
-        <v>141.4207567967531</v>
+        <v>237.1657016534233</v>
       </c>
       <c r="D5" t="n">
-        <v>173.7693436516855</v>
+        <v>135.1621151821796</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.96739100824416</v>
+        <v>40.6139207769863</v>
       </c>
       <c r="C6" t="n">
-        <v>207.0947694723434</v>
+        <v>279.9100149486251</v>
       </c>
       <c r="D6" t="n">
-        <v>86.54106012935635</v>
+        <v>66.17372225705202</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>174.6293546406056</v>
+        <v>220.9217041389555</v>
       </c>
       <c r="D7" t="n">
-        <v>43.11835917051991</v>
+        <v>38.26754376383641</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.507604620824606</v>
       </c>
       <c r="C8" t="n">
-        <v>111.5707178491288</v>
+        <v>140.6108149407494</v>
       </c>
       <c r="D8" t="n">
-        <v>34.13045893814036</v>
+        <v>33.04562772494764</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>56.46718270516377</v>
+        <v>60.68280734719958</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>32.50468473990763</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
         <v>14.44249047717483</v>
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.47210713921825</v>
+        <v>33.99988649347554</v>
       </c>
       <c r="D17" t="n">
         <v>4.722206457427158</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.567270246605409</v>
+        <v>2.138246499849553</v>
       </c>
       <c r="C2" t="n">
-        <v>2.89615572752809</v>
+        <v>4.721224709722911</v>
       </c>
       <c r="D2" t="n">
-        <v>11.50215610295563</v>
+        <v>11.11534750748239</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.4499435481813</v>
+        <v>11.16247139728623</v>
       </c>
       <c r="C3" t="n">
-        <v>10.18072369303943</v>
+        <v>26.76244241776805</v>
       </c>
       <c r="D3" t="n">
-        <v>81.48505945248526</v>
+        <v>82.6140693123691</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.3820073346058</v>
+        <v>31.4090543019682</v>
       </c>
       <c r="C4" t="n">
-        <v>39.6282460819225</v>
+        <v>81.33681554914399</v>
       </c>
       <c r="D4" t="n">
-        <v>193.9678209188593</v>
+        <v>177.2741829558466</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.83185307179588</v>
+        <v>51.51721078035138</v>
       </c>
       <c r="C5" t="n">
-        <v>125.8600556844411</v>
+        <v>227.3727683035613</v>
       </c>
       <c r="D5" t="n">
-        <v>194.6560260595364</v>
+        <v>154.5761760336603</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.74225198880216</v>
+        <v>47.2956956520901</v>
       </c>
       <c r="C6" t="n">
-        <v>223.839458315977</v>
+        <v>323.2207966691774</v>
       </c>
       <c r="D6" t="n">
-        <v>104.3322920257171</v>
+        <v>78.61148392215486</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C7" t="n">
-        <v>221.8200032883413</v>
+        <v>280.0297881685432</v>
       </c>
       <c r="D7" t="n">
-        <v>49.40645321622073</v>
+        <v>42.63926629084747</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>146.8694565553228</v>
+        <v>178.5799074024948</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>67.11718180083317</v>
+        <v>66.78436932909349</v>
       </c>
       <c r="D9" t="n">
-        <v>32.8374972116473</v>
+        <v>32.06093477758807</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.62361508084176</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.16670148773948</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.22516438163779</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
         <v>16.3902779224005</v>
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>3.719842051391165</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.863177216211199</v>
+        <v>3.517602024316322</v>
       </c>
       <c r="C2" t="n">
-        <v>4.092906179004952</v>
+        <v>10.32994934408494</v>
       </c>
       <c r="D2" t="n">
-        <v>12.88543861823939</v>
+        <v>14.46016193585127</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.10847527355266</v>
+        <v>9.267698328089891</v>
       </c>
       <c r="C3" t="n">
-        <v>10.72068493037517</v>
+        <v>23.01707492606647</v>
       </c>
       <c r="D3" t="n">
-        <v>73.06657288856887</v>
+        <v>74.87298866438299</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.02166486941822</v>
+        <v>26.59750880345459</v>
       </c>
       <c r="C4" t="n">
-        <v>32.99163160121406</v>
+        <v>74.11311594129596</v>
       </c>
       <c r="D4" t="n">
-        <v>190.8154290405228</v>
+        <v>175.219385010858</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.32839642596651</v>
+        <v>49.7746086053133</v>
       </c>
       <c r="C5" t="n">
-        <v>102.2490233973053</v>
+        <v>194.7051134447487</v>
       </c>
       <c r="D5" t="n">
-        <v>214.4136986075034</v>
+        <v>174.8983535115693</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.81774875103793</v>
+        <v>55.30577517103983</v>
       </c>
       <c r="C6" t="n">
-        <v>214.8230874001744</v>
+        <v>342.30008155351</v>
       </c>
       <c r="D6" t="n">
-        <v>131.8241729877405</v>
+        <v>99.42159000907451</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.97378021608837</v>
+        <v>28.68568617038755</v>
       </c>
       <c r="C7" t="n">
-        <v>265.2976821186156</v>
+        <v>350.7558745301877</v>
       </c>
       <c r="D7" t="n">
-        <v>62.34196096737671</v>
+        <v>50.90361846519711</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>208.6213871524472</v>
+        <v>249.010487705161</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>111.6031155233689</v>
+        <v>120.8109272414997</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>46.97662764820988</v>
       </c>
       <c r="D10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>27.36523550817559</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.52696183746906</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
         <v>16.65044106402591</v>
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.326562132615694</v>
+        <v>5.21406205725481</v>
       </c>
       <c r="C2" t="n">
-        <v>6.452045912310037</v>
+        <v>6.402958527097698</v>
       </c>
       <c r="D2" t="n">
-        <v>13.48430471782994</v>
+        <v>7.515278676009333</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.703733177495716</v>
+        <v>2.569233742013903</v>
       </c>
       <c r="C2" t="n">
-        <v>2.259983215176157</v>
+        <v>6.031857894892403</v>
       </c>
       <c r="D2" t="n">
-        <v>9.484664570728436</v>
+        <v>10.75799134313655</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.24654184695297</v>
+        <v>12.56146187583794</v>
       </c>
       <c r="C3" t="n">
-        <v>14.02426595516569</v>
+        <v>31.53373626040755</v>
       </c>
       <c r="D3" t="n">
-        <v>78.49072895453249</v>
+        <v>81.10217784782901</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.98858854711009</v>
+        <v>37.49687181600267</v>
       </c>
       <c r="C4" t="n">
-        <v>50.45103277353934</v>
+        <v>108.6490366812903</v>
       </c>
       <c r="D4" t="n">
-        <v>197.8732132863531</v>
+        <v>176.5722333473101</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.42346172236243</v>
+        <v>31.6122760767473</v>
       </c>
       <c r="C5" t="n">
-        <v>168.8360614378452</v>
+        <v>291.0881943091793</v>
       </c>
       <c r="D5" t="n">
-        <v>195.0241814486289</v>
+        <v>156.2206034382737</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.69564251615027</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="C6" t="n">
-        <v>221.0620940606628</v>
+        <v>291.3817368727491</v>
       </c>
       <c r="D6" t="n">
-        <v>101.1926628675358</v>
+        <v>76.88066271956774</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.407867265618931</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>146.7221943996858</v>
+        <v>175.1084475202781</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>82.19682653806419</v>
+        <v>89.03960803666446</v>
       </c>
       <c r="D8" t="n">
-        <v>25.03456645829366</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>35.83280945730432</v>
       </c>
       <c r="D9" t="n">
-        <v>20.85624822901923</v>
+        <v>20.52343575727956</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91890015564179</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.05884810899257</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
         <v>13.4519070435898</v>
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
         <v>2.5083653843506</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.888522730072368</v>
+        <v>6.842781498600268</v>
       </c>
       <c r="C2" t="n">
-        <v>4.16751900452771</v>
+        <v>6.863398200389452</v>
       </c>
       <c r="D2" t="n">
-        <v>18.1436793221853</v>
+        <v>12.13538337219482</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.198975988792613</v>
+        <v>11.07902284242526</v>
       </c>
       <c r="C3" t="n">
-        <v>16.25774198232718</v>
+        <v>16.13502351929633</v>
       </c>
       <c r="D3" t="n">
-        <v>14.46114368355552</v>
+        <v>9.44932165337555</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39783666637163</v>
+        <v>13.39871798554193</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14161548865147</v>
+        <v>70.1462294537195</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576216078396662</v>
+        <v>1.576319763004933</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.930917807804229</v>
+        <v>4.460079820393259</v>
       </c>
       <c r="C2" t="n">
-        <v>2.32674205906494</v>
+        <v>5.893431468593603</v>
       </c>
       <c r="D2" t="n">
-        <v>24.30807315715102</v>
+        <v>18.85151941694726</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.85031668506475</v>
+        <v>18.58448404139212</v>
       </c>
       <c r="C3" t="n">
-        <v>16.25283324380595</v>
+        <v>23.06125357275758</v>
       </c>
       <c r="D3" t="n">
-        <v>26.20775496486861</v>
+        <v>17.35729941108361</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.81002397146163</v>
+        <v>12.94139823738145</v>
       </c>
       <c r="C4" t="n">
-        <v>25.32123678793373</v>
+        <v>25.1170332654504</v>
       </c>
       <c r="D4" t="n">
-        <v>22.65382827549515</v>
+        <v>20.02470792352219</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.092505268377454</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.424156065963628</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
         <v>29.10881943091793</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>35.01894061048373</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4924,7 +4924,7 @@
         <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4938,7 +4938,7 @@
         <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44109649291264</v>
+        <v>15.44313290699228</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14506464467051</v>
+        <v>86.15642569164113</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250757156402661</v>
+        <v>3.251185875156269</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.636213570080939</v>
+        <v>4.772275590343745</v>
       </c>
       <c r="C2" t="n">
-        <v>3.805254101660637</v>
+        <v>6.343071917138642</v>
       </c>
       <c r="D2" t="n">
-        <v>31.09685853201772</v>
+        <v>19.80577818547515</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.5887708851076</v>
+        <v>16.81242943522663</v>
       </c>
       <c r="C3" t="n">
-        <v>11.88405595990764</v>
+        <v>22.98271375641783</v>
       </c>
       <c r="D3" t="n">
-        <v>39.56934121966769</v>
+        <v>28.40686982238146</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.99016682742431</v>
+        <v>25.89555919491812</v>
       </c>
       <c r="C4" t="n">
-        <v>34.3827680981318</v>
+        <v>44.32492709903924</v>
       </c>
       <c r="D4" t="n">
-        <v>30.69434197327653</v>
+        <v>24.2236428545858</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.03837027592364</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="C5" t="n">
-        <v>28.98610096788708</v>
+        <v>28.69157665661304</v>
       </c>
       <c r="D5" t="n">
-        <v>30.55689729468198</v>
+        <v>29.64878066825368</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.8302651248191</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5210,7 +5210,7 @@
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.38633523605029</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.62030998483051</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73610988328999</v>
+        <v>16.73850489844186</v>
       </c>
       <c r="C21" t="n">
-        <v>102.090270288069</v>
+        <v>102.1048798804954</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020832964986997</v>
+        <v>5.021551469532559</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.3711416899343</v>
+        <v>4.919537745980767</v>
       </c>
       <c r="C2" t="n">
-        <v>2.962914571416874</v>
+        <v>6.212499472473816</v>
       </c>
       <c r="D2" t="n">
-        <v>42.31627129615026</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18058482431918</v>
+        <v>16.56208377064369</v>
       </c>
       <c r="C3" t="n">
-        <v>13.54320958008475</v>
+        <v>23.9153740754523</v>
       </c>
       <c r="D3" t="n">
-        <v>54.39864029231576</v>
+        <v>37.13951565165684</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.48715214995145</v>
+        <v>29.63503620039422</v>
       </c>
       <c r="C4" t="n">
-        <v>31.46010518258904</v>
+        <v>51.26784686347268</v>
       </c>
       <c r="D4" t="n">
-        <v>42.6274853183965</v>
+        <v>32.3024447128328</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.40209995258047</v>
+        <v>25.13274122871835</v>
       </c>
       <c r="C5" t="n">
-        <v>47.98291904506286</v>
+        <v>57.94765824316799</v>
       </c>
       <c r="D5" t="n">
-        <v>34.80295611554943</v>
+        <v>31.83316931020283</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.781152377410974</v>
+        <v>10.90819874188631</v>
       </c>
       <c r="C6" t="n">
-        <v>29.98748362621883</v>
+        <v>29.78622534684823</v>
       </c>
       <c r="D6" t="n">
-        <v>38.60133798328035</v>
+        <v>38.15856976866503</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.40538935305847</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>40.22220344299182</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>41.82343394861835</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5560,7 +5560,7 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5574,7 +5574,7 @@
         <v>9.062513057902304</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,7 +5588,7 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
         <v>46.86470840992573</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>46.30903920932205</v>
@@ -5616,7 +5616,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06461672523193</v>
+        <v>18.06702121654423</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8501186360369</v>
+        <v>117.86580507936</v>
       </c>
       <c r="D21" t="n">
-        <v>6.881758752469305</v>
+        <v>6.882674749159706</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.35918079103409</v>
+        <v>5.723589115758905</v>
       </c>
       <c r="C2" t="n">
-        <v>9.535715451349269</v>
+        <v>8.148505945248527</v>
       </c>
       <c r="D2" t="n">
-        <v>33.54337381100077</v>
+        <v>29.36505558172634</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11047982669016</v>
+        <v>15.07473599870977</v>
       </c>
       <c r="C3" t="n">
-        <v>11.62389281828224</v>
+        <v>22.58019719767664</v>
       </c>
       <c r="D3" t="n">
-        <v>70.04278995948869</v>
+        <v>42.37223091529233</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.59452250261284</v>
+        <v>22.41133659254619</v>
       </c>
       <c r="C4" t="n">
-        <v>27.22288209105981</v>
+        <v>46.53287768589032</v>
       </c>
       <c r="D4" t="n">
-        <v>51.45928766580082</v>
+        <v>37.27990557336413</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.30959468420302</v>
+        <v>21.3775562599743</v>
       </c>
       <c r="C5" t="n">
-        <v>39.80986940720817</v>
+        <v>58.04583301359268</v>
       </c>
       <c r="D5" t="n">
-        <v>34.3366259560322</v>
+        <v>29.50151851261666</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.70694046251572</v>
+        <v>12.43776166510284</v>
       </c>
       <c r="C6" t="n">
-        <v>36.54850353370026</v>
+        <v>42.02272873258048</v>
       </c>
       <c r="D6" t="n">
-        <v>31.75855648468008</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,10 +5826,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>5.449681506274044</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>20.84054026575129</v>
       </c>
       <c r="D7" t="n">
         <v>30.72183090899544</v>
@@ -5846,7 +5846,7 @@
         <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.96562313481813</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
         <v>33.73775985644164</v>
@@ -5899,7 +5899,7 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.061614732675076</v>
+        <v>7.062579605296308</v>
       </c>
       <c r="C21" t="n">
-        <v>66.20263811882883</v>
+        <v>66.21168379965289</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296211049506307</v>
+        <v>5.296934703972231</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.169302573486956</v>
+        <v>4.321653394094459</v>
       </c>
       <c r="C2" t="n">
-        <v>8.112181280191393</v>
+        <v>9.408088249797183</v>
       </c>
       <c r="D2" t="n">
-        <v>27.15023276094554</v>
+        <v>33.60718741177681</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.05005343738336</v>
+        <v>18.16724126708723</v>
       </c>
       <c r="C3" t="n">
-        <v>28.4265047764664</v>
+        <v>28.66212422548563</v>
       </c>
       <c r="D3" t="n">
-        <v>81.9661158275662</v>
+        <v>57.56477663851173</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.73339089726815</v>
+        <v>27.04420400888689</v>
       </c>
       <c r="C4" t="n">
-        <v>28.49915410658066</v>
+        <v>53.04186496504667</v>
       </c>
       <c r="D4" t="n">
-        <v>77.48247406227101</v>
+        <v>51.53586398673207</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.85079971115027</v>
+        <v>28.59340188618836</v>
       </c>
       <c r="C5" t="n">
-        <v>46.43666641087414</v>
+        <v>75.54548584179207</v>
       </c>
       <c r="D5" t="n">
-        <v>46.31394794784328</v>
+        <v>37.11006322052944</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.99878157258428</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="C6" t="n">
-        <v>52.64916588334796</v>
+        <v>72.09071567054754</v>
       </c>
       <c r="D6" t="n">
-        <v>35.70321876034376</v>
+        <v>33.44912603139308</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>10.83947640258903</v>
       </c>
       <c r="C7" t="n">
-        <v>39.94436884268997</v>
+        <v>44.49575119957818</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>5.674501730546564</v>
       </c>
       <c r="C8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.28352946454485</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.06249736236907</v>
+        <v>31.17343485294896</v>
       </c>
     </row>
     <row r="10">
@@ -6182,7 +6182,7 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
         <v>34.16482010778901</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286145115583746</v>
+        <v>7.286741936415063</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59375557418137</v>
+        <v>75.59994759030629</v>
       </c>
       <c r="D21" t="n">
-        <v>6.375376976135778</v>
+        <v>6.37589919436318</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.219952543480291</v>
+        <v>5.096252332745193</v>
       </c>
       <c r="C2" t="n">
-        <v>5.071708640139023</v>
+        <v>8.918196145378026</v>
       </c>
       <c r="D2" t="n">
-        <v>28.88203571123691</v>
+        <v>33.91840143402305</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.73098543350315</v>
+        <v>16.3608254912731</v>
       </c>
       <c r="C3" t="n">
-        <v>30.38018270791754</v>
+        <v>33.48250545333747</v>
       </c>
       <c r="D3" t="n">
-        <v>84.66592201424493</v>
+        <v>71.09326000303278</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.70558316637975</v>
+        <v>31.68983414538279</v>
       </c>
       <c r="C4" t="n">
-        <v>54.05011985730815</v>
+        <v>64.09438061945727</v>
       </c>
       <c r="D4" t="n">
-        <v>100.4170821811807</v>
+        <v>68.80382435672921</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.95021827118646</v>
+        <v>35.51472320112837</v>
       </c>
       <c r="C5" t="n">
-        <v>50.11822030179968</v>
+        <v>87.71915737445252</v>
       </c>
       <c r="D5" t="n">
-        <v>64.59899893944014</v>
+        <v>46.92754026299754</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.73968229412113</v>
+        <v>31.15478164656829</v>
       </c>
       <c r="C6" t="n">
-        <v>64.64415933383549</v>
+        <v>99.09957676208155</v>
       </c>
       <c r="D6" t="n">
-        <v>42.50574860306991</v>
+        <v>37.95731148929444</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>59.82672334909638</v>
+        <v>77.6729331168949</v>
       </c>
       <c r="D7" t="n">
-        <v>36.35117224514665</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>9.012443924985718</v>
       </c>
       <c r="C8" t="n">
-        <v>40.63944621729671</v>
+        <v>43.47669708257</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.46425315758427</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6507,7 +6507,7 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>33.62976760897449</v>
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>32.00006641992479</v>
@@ -6594,7 +6594,7 @@
         <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.499116108221267</v>
+        <v>7.497677597045638</v>
       </c>
       <c r="C21" t="n">
-        <v>85.30244573101692</v>
+        <v>85.28608266639414</v>
       </c>
       <c r="D21" t="n">
-        <v>7.499116108221267</v>
+        <v>7.497677597045638</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_90_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_90_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497618819991</v>
+        <v>10.8449765107711</v>
       </c>
       <c r="C21" t="n">
-        <v>37.789071440092</v>
+        <v>37.78907256408392</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.14672237628928</v>
+        <v>0.9680032363873551</v>
       </c>
       <c r="C2" t="n">
-        <v>9.288315029879072</v>
+        <v>2.421971586376881</v>
       </c>
       <c r="D2" t="n">
-        <v>37.8728811867292</v>
+        <v>17.14327841155781</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8369731278328</v>
+        <v>8.70810213666921</v>
       </c>
       <c r="C3" t="n">
-        <v>34.40534829532947</v>
+        <v>31.48464887519521</v>
       </c>
       <c r="D3" t="n">
-        <v>80.38550202372883</v>
+        <v>79.77681844709582</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.42181702212341</v>
+        <v>14.40911105523044</v>
       </c>
       <c r="C4" t="n">
-        <v>74.03653962036472</v>
+        <v>80.89012034371169</v>
       </c>
       <c r="D4" t="n">
-        <v>86.09731016703677</v>
+        <v>88.16487083218057</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.52792788964008</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>103.9670818797373</v>
+        <v>74.6128255227576</v>
       </c>
       <c r="D5" t="n">
-        <v>60.254765348148</v>
+        <v>51.44357970253288</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>8.774860980557992</v>
       </c>
       <c r="C6" t="n">
-        <v>118.9838947638964</v>
+        <v>45.24286120251001</v>
       </c>
       <c r="D6" t="n">
-        <v>43.43153668817465</v>
+        <v>30.99377502307181</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.26647990067416</v>
+        <v>5.988660995905543</v>
       </c>
       <c r="C7" t="n">
-        <v>111.8083007935565</v>
+        <v>28.86534600026472</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.10418842983718</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>73.8519710519663</v>
+        <v>27.62147165898401</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.543749359432489</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>40.82499653339935</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>31.62994753542373</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>37.84931924182727</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.04125876577415</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>23.1456838753228</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>22.7323680918349</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>25.02769422436394</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.75262494072559</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>86.05902200657115</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.693696140893261</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>94.24777772594243</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.655408158504917</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.648976290236146</v>
+        <v>1.486366024229671</v>
       </c>
       <c r="C2" t="n">
-        <v>10.84536688881452</v>
+        <v>7.198174167537614</v>
       </c>
       <c r="D2" t="n">
-        <v>45.82601933883262</v>
+        <v>16.74370709592935</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.78574232076272</v>
+        <v>5.753041546886308</v>
       </c>
       <c r="C3" t="n">
-        <v>35.08766294978101</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="D3" t="n">
-        <v>89.80046250745575</v>
+        <v>74.98098091185015</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.34524070119216</v>
+        <v>16.0044510746315</v>
       </c>
       <c r="C4" t="n">
-        <v>79.89462817160542</v>
+        <v>80.53276417936586</v>
       </c>
       <c r="D4" t="n">
-        <v>103.5311858990516</v>
+        <v>108.3810195580309</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.98229715025711</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="C5" t="n">
-        <v>118.49694790259</v>
+        <v>116.5579961867026</v>
       </c>
       <c r="D5" t="n">
-        <v>73.99923320760334</v>
+        <v>71.3976017913493</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.49695393146069</v>
+        <v>12.47801332097696</v>
       </c>
       <c r="C6" t="n">
-        <v>141.0418021829138</v>
+        <v>85.13225217376218</v>
       </c>
       <c r="D6" t="n">
-        <v>51.32086123950202</v>
+        <v>39.7686360036298</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>37.60879105428681</v>
+        <v>8.204465564390594</v>
       </c>
       <c r="C7" t="n">
-        <v>139.416027984681</v>
+        <v>48.32849423695774</v>
       </c>
       <c r="D7" t="n">
-        <v>41.68108053150257</v>
+        <v>32.5184292077671</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.1138670381594</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>109.1507097581604</v>
+        <v>34.04701038327938</v>
       </c>
       <c r="D8" t="n">
-        <v>38.30288668118931</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.09374905798895</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>64.01093206459626</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>39.28954312395736</v>
+        <v>35.44600086183109</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.73780091417063</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.37527396939631</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>38.83695743229957</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>28.5776939229204</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.873395719737983</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3541443565938</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.84174464967248</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.172247816599698</v>
+        <v>0.7667449570167589</v>
       </c>
       <c r="C2" t="n">
-        <v>16.08102739556275</v>
+        <v>2.845104846907257</v>
       </c>
       <c r="D2" t="n">
-        <v>37.70205708619026</v>
+        <v>11.2792993740916</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.6679325962531</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C3" t="n">
-        <v>38.04763227808514</v>
+        <v>24.64186737659494</v>
       </c>
       <c r="D3" t="n">
-        <v>100.7714931024139</v>
+        <v>74.05813806985815</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.48112279500572</v>
+        <v>17.44663845217007</v>
       </c>
       <c r="C4" t="n">
-        <v>82.35783316156066</v>
+        <v>73.64089529555325</v>
       </c>
       <c r="D4" t="n">
-        <v>118.0934495961446</v>
+        <v>120.2503493023748</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.89041377668541</v>
+        <v>16.93514789825748</v>
       </c>
       <c r="C5" t="n">
-        <v>130.8669689760999</v>
+        <v>141.9361743414826</v>
       </c>
       <c r="D5" t="n">
-        <v>89.75628386076465</v>
+        <v>82.44226346412592</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.28690098048088</v>
+        <v>10.74719211838983</v>
       </c>
       <c r="C6" t="n">
-        <v>159.8795771320016</v>
+        <v>115.2404907676034</v>
       </c>
       <c r="D6" t="n">
-        <v>59.53219903782235</v>
+        <v>40.53341746523807</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.45393695892307</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>166.2452292463379</v>
+        <v>50.36463897556562</v>
       </c>
       <c r="D7" t="n">
-        <v>45.99291644855457</v>
+        <v>34.13536767666159</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.79113408536946</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>142.4466831476909</v>
+        <v>38.30288668118931</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>36.96770980341364</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.8640611529242</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>93.52030455884689</v>
+        <v>27.06874770149305</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>40.71405904281946</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>54.37900533823083</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>31.09685853201771</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>19.09302935219197</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>18.63357142660446</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.03576317579774</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4917436672189</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04917436672189</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.772676500971245</v>
+        <v>0.5811946409141118</v>
       </c>
       <c r="C2" t="n">
-        <v>11.06331487915731</v>
+        <v>3.581415625092364</v>
       </c>
       <c r="D2" t="n">
-        <v>31.12827445855362</v>
+        <v>13.64531134132642</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.41330008795468</v>
+        <v>4.236241343824987</v>
       </c>
       <c r="C3" t="n">
-        <v>58.60542920501334</v>
+        <v>16.76825078853552</v>
       </c>
       <c r="D3" t="n">
-        <v>105.8520374718911</v>
+        <v>66.60667299462486</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.55623434214721</v>
+        <v>14.74094177926586</v>
       </c>
       <c r="C4" t="n">
-        <v>110.3847666223986</v>
+        <v>67.56584050167397</v>
       </c>
       <c r="D4" t="n">
-        <v>109.3509862898267</v>
+        <v>129.7713385381604</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.45243112740432</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="C5" t="n">
-        <v>95.52405162321466</v>
+        <v>140.1690284738384</v>
       </c>
       <c r="D5" t="n">
-        <v>59.69026041820608</v>
+        <v>105.6360529769568</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.21641076775758</v>
+        <v>16.38242394076653</v>
       </c>
       <c r="C6" t="n">
-        <v>109.4845039776043</v>
+        <v>173.8066500644468</v>
       </c>
       <c r="D6" t="n">
-        <v>30.26924521733767</v>
+        <v>55.82904669740338</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.70269467652924</v>
+        <v>7.905032514595317</v>
       </c>
       <c r="C7" t="n">
-        <v>100.1304118515407</v>
+        <v>107.0772586067911</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>68.92850631516855</v>
+        <v>52.40569245269473</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>38.30288668118931</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>41.49062147687869</v>
+        <v>37.16405934426299</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>41.60155896745857</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.98534020436108</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.28094407433061</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>23.66110142005238</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.63872651149973</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.575525138866883</v>
+        <v>0.3298672286269283</v>
       </c>
       <c r="C2" t="n">
-        <v>5.180682635310418</v>
+        <v>3.048326621686346</v>
       </c>
       <c r="D2" t="n">
-        <v>22.24345773511998</v>
+        <v>9.806677817721388</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.8389776809703</v>
+        <v>3.249584901056942</v>
       </c>
       <c r="C3" t="n">
-        <v>51.82155256866788</v>
+        <v>15.47725255745097</v>
       </c>
       <c r="D3" t="n">
-        <v>107.5406435231956</v>
+        <v>63.53380268033234</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.83473189498382</v>
+        <v>12.37983855055228</v>
       </c>
       <c r="C4" t="n">
-        <v>131.6729838412865</v>
+        <v>56.36017220540089</v>
       </c>
       <c r="D4" t="n">
-        <v>130.9582715125948</v>
+        <v>133.727781786275</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.15223731408305</v>
+        <v>23.21833320543707</v>
       </c>
       <c r="C5" t="n">
-        <v>145.1759417654971</v>
+        <v>139.4572613882594</v>
       </c>
       <c r="D5" t="n">
-        <v>77.80350556155973</v>
+        <v>123.7738418129166</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.32837106377072</v>
+        <v>20.56859615167493</v>
       </c>
       <c r="C6" t="n">
-        <v>130.9386365585099</v>
+        <v>201.8620542087079</v>
       </c>
       <c r="D6" t="n">
-        <v>37.27303333943441</v>
+        <v>68.62907326537329</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>9.162651323735481</v>
       </c>
       <c r="C7" t="n">
-        <v>125.5223344741802</v>
+        <v>161.8735067193268</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>42.4596064609703</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.179341034707678</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>89.79064503041327</v>
+        <v>79.27612711792993</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>41.30703465618455</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>47.59218345877262</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.65044106402591</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.227004703859266</v>
+        <v>0.6067200812245288</v>
       </c>
       <c r="C2" t="n">
-        <v>3.769911184307752</v>
+        <v>9.367836593923064</v>
       </c>
       <c r="D2" t="n">
-        <v>21.51303744316036</v>
+        <v>19.53579756680728</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.98423528346982</v>
+        <v>2.154936210821749</v>
       </c>
       <c r="C3" t="n">
-        <v>35.44109212330985</v>
+        <v>13.44503480966007</v>
       </c>
       <c r="D3" t="n">
-        <v>100.8107630105837</v>
+        <v>57.07390278638832</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.11849803924015</v>
+        <v>9.418887474543899</v>
       </c>
       <c r="C4" t="n">
-        <v>130.3967118257656</v>
+        <v>47.51560713784138</v>
       </c>
       <c r="D4" t="n">
-        <v>151.2254711190659</v>
+        <v>135.0933928428823</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.48451000647497</v>
+        <v>21.622993186036</v>
       </c>
       <c r="C5" t="n">
-        <v>191.9316761802515</v>
+        <v>121.6385405561798</v>
       </c>
       <c r="D5" t="n">
-        <v>102.1508486268806</v>
+        <v>141.7643684932394</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.95731148929444</v>
+        <v>25.55980148006571</v>
       </c>
       <c r="C6" t="n">
-        <v>178.2745838664741</v>
+        <v>214.1790609061884</v>
       </c>
       <c r="D6" t="n">
-        <v>49.75104666041137</v>
+        <v>88.31213298781759</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.88908787161589</v>
+        <v>15.4507453694363</v>
       </c>
       <c r="C7" t="n">
-        <v>155.8848457234213</v>
+        <v>222.8380756576452</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>50.783845245279</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.01797455831271</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>123.9211039685536</v>
+        <v>141.6121975990812</v>
       </c>
       <c r="D8" t="n">
-        <v>29.6242369756475</v>
+        <v>43.30979997284804</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>73.44061876388687</v>
+        <v>70.66718149938963</v>
       </c>
       <c r="D9" t="n">
-        <v>29.39843500367073</v>
+        <v>43.37655881673681</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>41.99425804915732</v>
+        <v>43.98720588877834</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>33.05151821117311</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.947787445225672</v>
+        <v>0.3976078202199582</v>
       </c>
       <c r="C2" t="n">
-        <v>1.828014225307561</v>
+        <v>4.721224709722911</v>
       </c>
       <c r="D2" t="n">
-        <v>15.04332007217387</v>
+        <v>14.06549935874405</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.19883712007237</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C3" t="n">
-        <v>28.97628349084461</v>
+        <v>24.31789063419349</v>
       </c>
       <c r="D3" t="n">
-        <v>99.25469289935253</v>
+        <v>64.0492202250619</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.53890704083604</v>
+        <v>14.98343346221482</v>
       </c>
       <c r="C4" t="n">
-        <v>128.0738967575176</v>
+        <v>67.17019617686253</v>
       </c>
       <c r="D4" t="n">
-        <v>163.9754285541193</v>
+        <v>141.4875156406418</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.2761995667254</v>
+        <v>16.19883712007237</v>
       </c>
       <c r="C5" t="n">
-        <v>234.8831382410494</v>
+        <v>180.9851892778995</v>
       </c>
       <c r="D5" t="n">
-        <v>108.7285582453343</v>
+        <v>131.4805612912541</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.75855648468008</v>
+        <v>9.579894098040377</v>
       </c>
       <c r="C6" t="n">
-        <v>208.4230741161894</v>
+        <v>203.4318687877986</v>
       </c>
       <c r="D6" t="n">
-        <v>48.94601354292898</v>
+        <v>73.41902031439348</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>163.3107853583442</v>
+        <v>99.59143236190918</v>
       </c>
       <c r="D7" t="n">
-        <v>34.07548106670254</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>90.54168202416209</v>
+        <v>52.07189823325082</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>32.06093477758807</v>
+        <v>33.50312215512664</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>26.84687272033327</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.90832191507333</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>26.90479583488384</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>14.82929907264807</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.016910695150449</v>
+        <v>0.2572178985126644</v>
       </c>
       <c r="C2" t="n">
-        <v>9.619164006210248</v>
+        <v>2.670353755551324</v>
       </c>
       <c r="D2" t="n">
-        <v>13.80533621711865</v>
+        <v>9.872454913905925</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.67298020349457</v>
+        <v>2.267837196810132</v>
       </c>
       <c r="C3" t="n">
-        <v>18.04452280405637</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D3" t="n">
-        <v>89.6630178288612</v>
+        <v>60.92235378703582</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.53141291210056</v>
+        <v>9.942159000907449</v>
       </c>
       <c r="C4" t="n">
-        <v>102.331490204462</v>
+        <v>61.24829402484576</v>
       </c>
       <c r="D4" t="n">
-        <v>173.4326041891288</v>
+        <v>135.7060034103324</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.35107443415542</v>
+        <v>15.4379826492811</v>
       </c>
       <c r="C5" t="n">
-        <v>237.1657016534233</v>
+        <v>138.3773389135879</v>
       </c>
       <c r="D5" t="n">
-        <v>135.1621151821796</v>
+        <v>135.4811831860599</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.6139207769863</v>
+        <v>9.620145753914496</v>
       </c>
       <c r="C6" t="n">
-        <v>279.9100149486251</v>
+        <v>202.7878422938127</v>
       </c>
       <c r="D6" t="n">
-        <v>66.17372225705202</v>
+        <v>79.69827863075608</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>3.712969817461437</v>
       </c>
       <c r="C7" t="n">
-        <v>220.9217041389555</v>
+        <v>135.4036251174243</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>140.6108149407494</v>
+        <v>57.24570863463151</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>60.68280734719958</v>
+        <v>30.28593492830985</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>21.41093568191868</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>19.50241814486289</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>20.64124548178919</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>14.03801042302514</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.60978849752428</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.585383673638358</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.138246499849553</v>
+        <v>0.3171045084717197</v>
       </c>
       <c r="C2" t="n">
-        <v>4.721224709722911</v>
+        <v>7.915831739342032</v>
       </c>
       <c r="D2" t="n">
-        <v>11.11534750748239</v>
+        <v>14.20294403733861</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.16247139728623</v>
+        <v>1.497165248976386</v>
       </c>
       <c r="C3" t="n">
-        <v>26.76244241776805</v>
+        <v>14.69676313257475</v>
       </c>
       <c r="D3" t="n">
-        <v>82.6140693123691</v>
+        <v>54.68334712654734</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.4090543019682</v>
+        <v>7.032258805519903</v>
       </c>
       <c r="C4" t="n">
-        <v>81.33681554914399</v>
+        <v>56.30912132478006</v>
       </c>
       <c r="D4" t="n">
-        <v>177.2741829558466</v>
+        <v>135.9357323731261</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.51721078035138</v>
+        <v>15.60978849752429</v>
       </c>
       <c r="C5" t="n">
-        <v>227.3727683035613</v>
+        <v>125.5409876805609</v>
       </c>
       <c r="D5" t="n">
-        <v>154.5761760336603</v>
+        <v>154.2325643371739</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.2956956520901</v>
+        <v>15.37613254391355</v>
       </c>
       <c r="C6" t="n">
-        <v>323.2207966691774</v>
+        <v>213.011762885839</v>
       </c>
       <c r="D6" t="n">
-        <v>78.61148392215486</v>
+        <v>103.2052456612417</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.86995163914969</v>
+        <v>7.425939634922873</v>
       </c>
       <c r="C7" t="n">
-        <v>280.0297881685432</v>
+        <v>221.4007970186279</v>
       </c>
       <c r="D7" t="n">
-        <v>42.63926629084747</v>
+        <v>50.90361846519711</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>178.5799074024948</v>
+        <v>120.8335074386974</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>66.78436932909349</v>
+        <v>51.14218315732908</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>23.40781051235669</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>27.90126975469435</v>
       </c>
       <c r="D10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>17.94732978133594</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>18.48041878474196</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.517602024316322</v>
+        <v>0.3838633523605028</v>
       </c>
       <c r="C2" t="n">
-        <v>10.32994934408494</v>
+        <v>8.265333922053896</v>
       </c>
       <c r="D2" t="n">
-        <v>14.46016193585127</v>
+        <v>11.9586687854304</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.267698328089891</v>
+        <v>1.281180754042087</v>
       </c>
       <c r="C3" t="n">
-        <v>23.01707492606647</v>
+        <v>23.76320318129405</v>
       </c>
       <c r="D3" t="n">
-        <v>74.87298866438299</v>
+        <v>53.83904410089508</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.59750880345459</v>
+        <v>4.837070938824034</v>
       </c>
       <c r="C4" t="n">
-        <v>74.11311594129596</v>
+        <v>45.57567367424968</v>
       </c>
       <c r="D4" t="n">
-        <v>175.219385010858</v>
+        <v>131.5708820800448</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.7746086053133</v>
+        <v>13.42539985557513</v>
       </c>
       <c r="C5" t="n">
-        <v>194.7051134447487</v>
+        <v>114.1281706186917</v>
       </c>
       <c r="D5" t="n">
-        <v>174.8983535115693</v>
+        <v>168.0506632744478</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.30577517103983</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="C6" t="n">
-        <v>342.30008155351</v>
+        <v>207.2557760958399</v>
       </c>
       <c r="D6" t="n">
-        <v>99.42159000907451</v>
+        <v>126.2291928212379</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.68568617038755</v>
+        <v>12.69596131131975</v>
       </c>
       <c r="C7" t="n">
-        <v>350.7558745301877</v>
+        <v>267.1541670273463</v>
       </c>
       <c r="D7" t="n">
-        <v>50.90361846519711</v>
+        <v>65.93515756492003</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>249.010487705161</v>
+        <v>207.2027617198106</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>120.8109272414997</v>
+        <v>99.39999155958103</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>46.97662764820988</v>
+        <v>43.70249905454677</v>
       </c>
       <c r="D10" t="n">
-        <v>26.90479583488384</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.52696183746906</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>8.958447801252145</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.27884171020187</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.21406205725481</v>
+        <v>2.601631416254047</v>
       </c>
       <c r="C2" t="n">
-        <v>6.402958527097698</v>
+        <v>3.586324363613598</v>
       </c>
       <c r="D2" t="n">
-        <v>7.515278676009333</v>
+        <v>13.89860224902209</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.569233742013903</v>
+        <v>0.6567892141411161</v>
       </c>
       <c r="C2" t="n">
-        <v>6.031857894892403</v>
+        <v>22.22578627644354</v>
       </c>
       <c r="D2" t="n">
-        <v>10.75799134313655</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.56146187583794</v>
+        <v>1.271363276999619</v>
       </c>
       <c r="C3" t="n">
-        <v>31.53373626040755</v>
+        <v>27.93563092434299</v>
       </c>
       <c r="D3" t="n">
-        <v>81.10217784782901</v>
+        <v>51.02633692822797</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.49687181600267</v>
+        <v>3.624612524079224</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6490366812903</v>
+        <v>52.40372895728624</v>
       </c>
       <c r="D4" t="n">
-        <v>176.5722333473101</v>
+        <v>128.9417617280718</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.6122760767473</v>
+        <v>10.84831213192726</v>
       </c>
       <c r="C5" t="n">
-        <v>291.0881943091793</v>
+        <v>99.54921721062659</v>
       </c>
       <c r="D5" t="n">
-        <v>156.2206034382737</v>
+        <v>174.3583922742336</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.7912318963607</v>
+        <v>18.43525839034661</v>
       </c>
       <c r="C6" t="n">
-        <v>291.3817368727491</v>
+        <v>194.3349945602477</v>
       </c>
       <c r="D6" t="n">
-        <v>76.88066271956774</v>
+        <v>147.4418154668988</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>16.94791061841269</v>
       </c>
       <c r="C7" t="n">
-        <v>175.1084475202781</v>
+        <v>285.180036625022</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>82.52374852357838</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>8.762098260402782</v>
       </c>
       <c r="C8" t="n">
-        <v>89.03960803666446</v>
+        <v>276.631959364145</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>44.81187396034566</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>35.83280945730432</v>
+        <v>169.0687356437516</v>
       </c>
       <c r="D9" t="n">
-        <v>20.52343575727956</v>
+        <v>28.73281006019139</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>76.44378499117791</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.63727743324319</v>
+        <v>35.7169632282032</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>15.83853571261379</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>10.6666888066416</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.842781498600268</v>
+        <v>3.137665662772806</v>
       </c>
       <c r="C2" t="n">
-        <v>6.863398200389452</v>
+        <v>5.96804429411636</v>
       </c>
       <c r="D2" t="n">
-        <v>12.13538337219482</v>
+        <v>22.09030509325748</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.07902284242526</v>
+        <v>4.309872421643497</v>
       </c>
       <c r="C3" t="n">
-        <v>16.13502351929633</v>
+        <v>7.078400947619503</v>
       </c>
       <c r="D3" t="n">
-        <v>9.44932165337555</v>
+        <v>12.48292205949819</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39871798554193</v>
+        <v>11.67840297373722</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1462294537195</v>
+        <v>59.94913526518438</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576319763004933</v>
+        <v>0.7785601982491478</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.460079820393259</v>
+        <v>1.707259257685203</v>
       </c>
       <c r="C2" t="n">
-        <v>5.893431468593603</v>
+        <v>3.577488634275377</v>
       </c>
       <c r="D2" t="n">
-        <v>18.85151941694726</v>
+        <v>18.07397523518378</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.58448404139212</v>
+        <v>8.462665210607506</v>
       </c>
       <c r="C3" t="n">
-        <v>23.06125357275758</v>
+        <v>17.89235190989812</v>
       </c>
       <c r="D3" t="n">
-        <v>17.35729941108361</v>
+        <v>28.78484268851648</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.94139823738145</v>
+        <v>5.526257827205296</v>
       </c>
       <c r="C4" t="n">
-        <v>25.1170332654504</v>
+        <v>12.08629598698248</v>
       </c>
       <c r="D4" t="n">
-        <v>20.02470792352219</v>
+        <v>20.84152201345554</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.44489594093983</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.35572113076938</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44313290699228</v>
+        <v>13.63117310481327</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15642569164113</v>
+        <v>73.76870150840124</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251185875156269</v>
+        <v>1.603667424095679</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.772275590343745</v>
+        <v>2.125483779694344</v>
       </c>
       <c r="C2" t="n">
-        <v>6.343071917138642</v>
+        <v>3.62559427178347</v>
       </c>
       <c r="D2" t="n">
-        <v>19.80577818547515</v>
+        <v>19.0979380907132</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.81242943522663</v>
+        <v>7.004769869800993</v>
       </c>
       <c r="C3" t="n">
-        <v>22.98271375641783</v>
+        <v>15.36926030998382</v>
       </c>
       <c r="D3" t="n">
-        <v>28.40686982238146</v>
+        <v>37.01188845010475</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.89555919491812</v>
+        <v>12.23944862884498</v>
       </c>
       <c r="C4" t="n">
-        <v>44.32492709903924</v>
+        <v>32.65980087717864</v>
       </c>
       <c r="D4" t="n">
-        <v>24.2236428545858</v>
+        <v>30.88578277560466</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.70734137314322</v>
+        <v>5.743224069843841</v>
       </c>
       <c r="C5" t="n">
-        <v>28.69157665661304</v>
+        <v>15.58524480491812</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>27.66074156715389</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="C9" t="n">
-        <v>29.62030998483051</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73850489844186</v>
+        <v>14.84738769315689</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1048798804954</v>
+        <v>87.43461641525727</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021551469532559</v>
+        <v>2.474564615526149</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.919537745980767</v>
+        <v>2.440624792757571</v>
       </c>
       <c r="C2" t="n">
-        <v>6.212499472473816</v>
+        <v>5.497787143782138</v>
       </c>
       <c r="D2" t="n">
-        <v>21.26269177857742</v>
+        <v>25.09739831136546</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56208377064369</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C3" t="n">
-        <v>23.9153740754523</v>
+        <v>14.59858836215007</v>
       </c>
       <c r="D3" t="n">
-        <v>37.13951565165684</v>
+        <v>44.10992435180919</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.63503620039422</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C4" t="n">
-        <v>51.26784686347268</v>
+        <v>36.24612524079224</v>
       </c>
       <c r="D4" t="n">
-        <v>32.3024447128328</v>
+        <v>43.11246868429443</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.13274122871835</v>
+        <v>12.61545799957152</v>
       </c>
       <c r="C5" t="n">
-        <v>57.94765824316799</v>
+        <v>41.99425804915732</v>
       </c>
       <c r="D5" t="n">
-        <v>31.83316931020283</v>
+        <v>32.88854809226815</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.90819874188631</v>
+        <v>6.31950997223672</v>
       </c>
       <c r="C6" t="n">
-        <v>29.78622534684823</v>
+        <v>18.55601335796896</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>33.77113927838603</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.48689010804419</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.27499683484289</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>27.61656292046278</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>42.74234979979338</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.06702121654423</v>
+        <v>16.10120354659931</v>
       </c>
       <c r="C21" t="n">
-        <v>117.86580507936</v>
+        <v>101.6918118732588</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882674749159706</v>
+        <v>3.38972706244196</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.723589115758905</v>
+        <v>2.250165738133689</v>
       </c>
       <c r="C2" t="n">
-        <v>8.148505945248527</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="D2" t="n">
-        <v>29.36505558172634</v>
+        <v>34.74797824411161</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.07473599870977</v>
+        <v>7.898160280665589</v>
       </c>
       <c r="C3" t="n">
-        <v>22.58019719767664</v>
+        <v>18.6384801651257</v>
       </c>
       <c r="D3" t="n">
-        <v>42.37223091529233</v>
+        <v>53.95194508688346</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.41133659254619</v>
+        <v>13.68163600638355</v>
       </c>
       <c r="C4" t="n">
-        <v>46.53287768589032</v>
+        <v>36.43756604312036</v>
       </c>
       <c r="D4" t="n">
-        <v>37.27990557336413</v>
+        <v>55.54335811546755</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21.3775562599743</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C5" t="n">
-        <v>58.04583301359268</v>
+        <v>56.00870652728054</v>
       </c>
       <c r="D5" t="n">
-        <v>29.50151851261666</v>
+        <v>40.98796665230434</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.43776166510284</v>
+        <v>11.91449013873929</v>
       </c>
       <c r="C6" t="n">
-        <v>42.02272873258048</v>
+        <v>44.39757642915352</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>36.4277485660779</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>20.84054026575129</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.162496759482</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.31775176547326</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.55661955724149</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.062579605296308</v>
+        <v>17.38618705446433</v>
       </c>
       <c r="C21" t="n">
-        <v>66.21168379965289</v>
+        <v>115.6181439121878</v>
       </c>
       <c r="D21" t="n">
-        <v>5.296934703972231</v>
+        <v>4.346546763616082</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.321653394094459</v>
+        <v>2.07148765596077</v>
       </c>
       <c r="C2" t="n">
-        <v>9.408088249797183</v>
+        <v>10.74522862298134</v>
       </c>
       <c r="D2" t="n">
-        <v>33.60718741177681</v>
+        <v>32.27004703859266</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.16724126708723</v>
+        <v>7.770533079113505</v>
       </c>
       <c r="C3" t="n">
-        <v>28.66212422548563</v>
+        <v>23.33123419142545</v>
       </c>
       <c r="D3" t="n">
-        <v>57.56477663851173</v>
+        <v>68.35909264670541</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.04420400888689</v>
+        <v>14.57502641724815</v>
       </c>
       <c r="C4" t="n">
-        <v>53.04186496504667</v>
+        <v>42.0148747509465</v>
       </c>
       <c r="D4" t="n">
-        <v>51.53586398673207</v>
+        <v>69.30157044278235</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.59340188618836</v>
+        <v>18.57957530287089</v>
       </c>
       <c r="C5" t="n">
-        <v>75.54548584179207</v>
+        <v>61.99736752318609</v>
       </c>
       <c r="D5" t="n">
-        <v>37.11006322052944</v>
+        <v>51.0999680060465</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>22.13841073076558</v>
+        <v>17.26796036999715</v>
       </c>
       <c r="C6" t="n">
-        <v>72.09071567054754</v>
+        <v>66.69699378341556</v>
       </c>
       <c r="D6" t="n">
-        <v>33.44912603139308</v>
+        <v>40.57366912111219</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.83947640258903</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>44.49575119957818</v>
+        <v>43.77711188006952</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>8.094509821514951</v>
       </c>
       <c r="C8" t="n">
-        <v>24.28352946454485</v>
+        <v>27.95526587842792</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>43.4472446514426</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>31.34327720578367</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.56719779780995</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>32.1031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.56809743005619</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.286741936415063</v>
+        <v>18.69567854034709</v>
       </c>
       <c r="C21" t="n">
-        <v>75.59994759030629</v>
+        <v>129.9794793757464</v>
       </c>
       <c r="D21" t="n">
-        <v>6.37589919436318</v>
+        <v>5.341622440099168</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.096252332745193</v>
+        <v>1.882010349041136</v>
       </c>
       <c r="C2" t="n">
-        <v>8.918196145378026</v>
+        <v>6.447137173788803</v>
       </c>
       <c r="D2" t="n">
-        <v>33.91840143402305</v>
+        <v>24.91381149067131</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.3608254912731</v>
+        <v>10.26908098642164</v>
       </c>
       <c r="C3" t="n">
-        <v>33.48250545333747</v>
+        <v>38.2587080344982</v>
       </c>
       <c r="D3" t="n">
-        <v>71.09326000303278</v>
+        <v>77.29299675535138</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>8.921141388490765</v>
       </c>
       <c r="C4" t="n">
-        <v>64.09438061945727</v>
+        <v>57.96827494495717</v>
       </c>
       <c r="D4" t="n">
-        <v>68.80382435672921</v>
+        <v>65.4982798365302</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.51472320112837</v>
+        <v>9.719302272043425</v>
       </c>
       <c r="C5" t="n">
-        <v>87.71915737445252</v>
+        <v>39.83441309981433</v>
       </c>
       <c r="D5" t="n">
-        <v>46.92754026299754</v>
+        <v>39.44171401811561</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.15478164656829</v>
+        <v>6.601271563355554</v>
       </c>
       <c r="C6" t="n">
-        <v>99.09957676208155</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>26.12332466230338</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.40326162673396</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>77.6729331168949</v>
+        <v>19.64280806657018</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.012443924985718</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>43.47669708257</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>27.5124976638126</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>33.62976760897449</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.34153469455343</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>34.72343455150544</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>32.25041208450772</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>27.38879745307752</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>26.9165768073348</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>31.29418982057133</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>98.18458790172348</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.497677597045638</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>85.28608266639414</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.497677597045638</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
